--- a/research/UNITEDHEALTH.xlsx
+++ b/research/UNITEDHEALTH.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpilc\OneDrive - Louisiana State University\Desktop\models\research\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpilc\OneDrive - Louisiana State University\Desktop\valuation\research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5045C54-AD0C-49B3-8623-5D28CEE44CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145A06D0-0394-482A-A258-660E22011279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{4E2427E6-D2C1-49DA-B21C-AD4FF0F49230}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="3" xr2:uid="{4E2427E6-D2C1-49DA-B21C-AD4FF0F49230}"/>
   </bookViews>
   <sheets>
     <sheet name="MAIN" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="BS - Q" sheetId="5" r:id="rId5"/>
     <sheet name="BS - Y" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateCount="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -193,15 +193,14 @@
     <t>CURR PRICE</t>
   </si>
   <si>
-    <t>UNDERVAL</t>
+    <t>WITH THAT EXTREMELY CONSERVATIVE GROWTH RATE, USING A ONE-TIME LOW NET INCOME AS THE BASE FOR THE GROWTH, THE COMPANY IS FAIRLY VALUED AT 325 A SHARE. THIS ISNT A DCF I MADE USING MY OWN ASSUMPTIONS, INSTEAD I START WITH THE CURRENT VALUATION THAT THE MARKET HAS GIVEN IT, THEN I BASICALLY SOLVE FOR WHAT THE MARKET'S IMPLICIT ASSUMPTIONS ARE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;Q&quot;#"/>
     <numFmt numFmtId="165" formatCode="&quot;FY&quot;\ #"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -270,7 +269,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -458,12 +457,92 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -571,15 +650,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -591,21 +681,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -683,14 +788,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>92</xdr:row>
       <xdr:rowOff>125406</xdr:rowOff>
     </xdr:to>
@@ -707,8 +812,58 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5715000" y="0"/>
-          <a:ext cx="0" cy="16996086"/>
+          <a:off x="6822908" y="0"/>
+          <a:ext cx="0" cy="16794156"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>125406</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F177F706-ED78-4AA7-8804-4C2221C9FC84}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15149763" y="0"/>
+          <a:ext cx="0" cy="16794156"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1206,7 +1361,7 @@
       <c r="C6" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="63" t="s">
         <v>39</v>
       </c>
       <c r="E6" s="36">
@@ -1220,7 +1375,7 @@
       <c r="C7" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="57"/>
+      <c r="D7" s="64"/>
       <c r="E7" s="36">
         <f>E5*E6</f>
         <v>280641.05519175</v>
@@ -1231,7 +1386,7 @@
       <c r="C8" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="57"/>
+      <c r="D8" s="64"/>
       <c r="E8" s="36">
         <f>28596+3424</f>
         <v>32020</v>
@@ -1244,7 +1399,7 @@
       <c r="C9" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="57"/>
+      <c r="D9" s="64"/>
       <c r="E9" s="36">
         <f>73495+5698</f>
         <v>79193</v>
@@ -1257,7 +1412,7 @@
       <c r="C10" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="58"/>
+      <c r="D10" s="65"/>
       <c r="E10" s="37">
         <f>E7-E8+E9</f>
         <v>327814.05519175</v>
@@ -2862,18 +3017,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0888499-3247-4B46-B85D-44CAD6C9F224}">
-  <dimension ref="A1:CB44"/>
+  <dimension ref="A1:CB49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="6.15625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.83984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.26171875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="14" width="7.26171875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.15625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.26171875" bestFit="1" customWidth="1"/>
-    <col min="17" max="27" width="7.26171875" bestFit="1" customWidth="1"/>
-    <col min="28" max="100" width="6.83984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.3125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="18" width="7.83984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.47265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="79" width="6.83984375" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="7.83984375" bestFit="1" customWidth="1"/>
+    <col min="81" max="100" width="6.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
@@ -3120,311 +3274,234 @@
         <v>2019</v>
       </c>
       <c r="D2" s="15">
-        <f>C2+1</f>
         <v>2020</v>
       </c>
       <c r="E2" s="15">
-        <f t="shared" ref="E2:G2" si="0">D2+1</f>
         <v>2021</v>
       </c>
       <c r="F2" s="15">
-        <f t="shared" si="0"/>
         <v>2022</v>
       </c>
       <c r="G2" s="15">
-        <f t="shared" si="0"/>
         <v>2023</v>
       </c>
       <c r="H2" s="15">
-        <f>G2+1</f>
         <v>2024</v>
       </c>
       <c r="I2" s="15">
-        <f t="shared" ref="I2:M2" si="1">H2+1</f>
         <v>2025</v>
       </c>
       <c r="J2" s="15">
-        <f t="shared" si="1"/>
         <v>2026</v>
       </c>
       <c r="K2" s="15">
-        <f t="shared" si="1"/>
         <v>2027</v>
       </c>
       <c r="L2" s="15">
-        <f t="shared" si="1"/>
         <v>2028</v>
       </c>
       <c r="M2" s="15">
-        <f t="shared" si="1"/>
         <v>2029</v>
       </c>
       <c r="N2" s="15">
-        <f t="shared" ref="N2" si="2">M2+1</f>
         <v>2030</v>
       </c>
       <c r="O2" s="15">
-        <f t="shared" ref="O2" si="3">N2+1</f>
         <v>2031</v>
       </c>
       <c r="P2" s="15">
-        <f t="shared" ref="P2" si="4">O2+1</f>
         <v>2032</v>
       </c>
       <c r="Q2" s="15">
-        <f t="shared" ref="Q2" si="5">P2+1</f>
         <v>2033</v>
       </c>
       <c r="R2" s="15">
-        <f t="shared" ref="R2" si="6">Q2+1</f>
         <v>2034</v>
       </c>
       <c r="S2" s="15">
-        <f t="shared" ref="S2" si="7">R2+1</f>
         <v>2035</v>
       </c>
       <c r="T2" s="15">
-        <f t="shared" ref="T2" si="8">S2+1</f>
         <v>2036</v>
       </c>
       <c r="U2" s="15">
-        <f t="shared" ref="U2" si="9">T2+1</f>
         <v>2037</v>
       </c>
       <c r="V2" s="15">
-        <f t="shared" ref="V2" si="10">U2+1</f>
         <v>2038</v>
       </c>
       <c r="W2" s="15">
-        <f t="shared" ref="W2" si="11">V2+1</f>
         <v>2039</v>
       </c>
       <c r="X2" s="15">
-        <f t="shared" ref="X2" si="12">W2+1</f>
         <v>2040</v>
       </c>
       <c r="Y2" s="15">
-        <f t="shared" ref="Y2" si="13">X2+1</f>
         <v>2041</v>
       </c>
       <c r="Z2" s="15">
-        <f t="shared" ref="Z2" si="14">Y2+1</f>
         <v>2042</v>
       </c>
       <c r="AA2" s="15">
-        <f t="shared" ref="AA2" si="15">Z2+1</f>
         <v>2043</v>
       </c>
       <c r="AB2" s="15">
-        <f t="shared" ref="AB2" si="16">AA2+1</f>
         <v>2044</v>
       </c>
       <c r="AC2" s="15">
-        <f t="shared" ref="AC2" si="17">AB2+1</f>
         <v>2045</v>
       </c>
       <c r="AD2" s="15">
-        <f t="shared" ref="AD2" si="18">AC2+1</f>
         <v>2046</v>
       </c>
       <c r="AE2" s="15">
-        <f t="shared" ref="AE2" si="19">AD2+1</f>
         <v>2047</v>
       </c>
       <c r="AF2" s="15">
-        <f t="shared" ref="AF2" si="20">AE2+1</f>
         <v>2048</v>
       </c>
       <c r="AG2" s="15">
-        <f t="shared" ref="AG2" si="21">AF2+1</f>
         <v>2049</v>
       </c>
       <c r="AH2" s="15">
-        <f t="shared" ref="AH2" si="22">AG2+1</f>
         <v>2050</v>
       </c>
       <c r="AI2" s="15">
-        <f t="shared" ref="AI2" si="23">AH2+1</f>
         <v>2051</v>
       </c>
       <c r="AJ2" s="15">
-        <f t="shared" ref="AJ2" si="24">AI2+1</f>
         <v>2052</v>
       </c>
       <c r="AK2" s="15">
-        <f t="shared" ref="AK2" si="25">AJ2+1</f>
         <v>2053</v>
       </c>
       <c r="AL2" s="15">
-        <f t="shared" ref="AL2" si="26">AK2+1</f>
         <v>2054</v>
       </c>
       <c r="AM2" s="15">
-        <f t="shared" ref="AM2" si="27">AL2+1</f>
         <v>2055</v>
       </c>
       <c r="AN2" s="15">
-        <f t="shared" ref="AN2" si="28">AM2+1</f>
         <v>2056</v>
       </c>
       <c r="AO2" s="15">
-        <f t="shared" ref="AO2" si="29">AN2+1</f>
         <v>2057</v>
       </c>
       <c r="AP2" s="15">
-        <f t="shared" ref="AP2" si="30">AO2+1</f>
         <v>2058</v>
       </c>
       <c r="AQ2" s="15">
-        <f t="shared" ref="AQ2" si="31">AP2+1</f>
         <v>2059</v>
       </c>
       <c r="AR2" s="15">
-        <f t="shared" ref="AR2" si="32">AQ2+1</f>
         <v>2060</v>
       </c>
       <c r="AS2" s="15">
-        <f t="shared" ref="AS2" si="33">AR2+1</f>
         <v>2061</v>
       </c>
       <c r="AT2" s="15">
-        <f t="shared" ref="AT2" si="34">AS2+1</f>
         <v>2062</v>
       </c>
       <c r="AU2" s="15">
-        <f t="shared" ref="AU2" si="35">AT2+1</f>
         <v>2063</v>
       </c>
       <c r="AV2" s="15">
-        <f t="shared" ref="AV2" si="36">AU2+1</f>
         <v>2064</v>
       </c>
       <c r="AW2" s="15">
-        <f t="shared" ref="AW2" si="37">AV2+1</f>
         <v>2065</v>
       </c>
       <c r="AX2" s="15">
-        <f t="shared" ref="AX2" si="38">AW2+1</f>
         <v>2066</v>
       </c>
       <c r="AY2" s="15">
-        <f t="shared" ref="AY2" si="39">AX2+1</f>
         <v>2067</v>
       </c>
       <c r="AZ2" s="15">
-        <f t="shared" ref="AZ2" si="40">AY2+1</f>
         <v>2068</v>
       </c>
       <c r="BA2" s="15">
-        <f t="shared" ref="BA2" si="41">AZ2+1</f>
         <v>2069</v>
       </c>
       <c r="BB2" s="15">
-        <f t="shared" ref="BB2" si="42">BA2+1</f>
         <v>2070</v>
       </c>
       <c r="BC2" s="15">
-        <f t="shared" ref="BC2" si="43">BB2+1</f>
         <v>2071</v>
       </c>
       <c r="BD2" s="15">
-        <f t="shared" ref="BD2" si="44">BC2+1</f>
         <v>2072</v>
       </c>
       <c r="BE2" s="15">
-        <f t="shared" ref="BE2" si="45">BD2+1</f>
         <v>2073</v>
       </c>
       <c r="BF2" s="15">
-        <f t="shared" ref="BF2" si="46">BE2+1</f>
         <v>2074</v>
       </c>
       <c r="BG2" s="15">
-        <f t="shared" ref="BG2" si="47">BF2+1</f>
         <v>2075</v>
       </c>
       <c r="BH2" s="15">
-        <f t="shared" ref="BH2" si="48">BG2+1</f>
         <v>2076</v>
       </c>
       <c r="BI2" s="15">
-        <f t="shared" ref="BI2" si="49">BH2+1</f>
         <v>2077</v>
       </c>
       <c r="BJ2" s="15">
-        <f t="shared" ref="BJ2" si="50">BI2+1</f>
         <v>2078</v>
       </c>
       <c r="BK2" s="15">
-        <f t="shared" ref="BK2" si="51">BJ2+1</f>
         <v>2079</v>
       </c>
       <c r="BL2" s="15">
-        <f t="shared" ref="BL2" si="52">BK2+1</f>
         <v>2080</v>
       </c>
       <c r="BM2" s="15">
-        <f t="shared" ref="BM2" si="53">BL2+1</f>
         <v>2081</v>
       </c>
       <c r="BN2" s="15">
-        <f t="shared" ref="BN2" si="54">BM2+1</f>
         <v>2082</v>
       </c>
       <c r="BO2" s="15">
-        <f t="shared" ref="BO2" si="55">BN2+1</f>
         <v>2083</v>
       </c>
       <c r="BP2" s="15">
-        <f t="shared" ref="BP2" si="56">BO2+1</f>
         <v>2084</v>
       </c>
       <c r="BQ2" s="15">
-        <f t="shared" ref="BQ2" si="57">BP2+1</f>
         <v>2085</v>
       </c>
       <c r="BR2" s="15">
-        <f t="shared" ref="BR2" si="58">BQ2+1</f>
         <v>2086</v>
       </c>
       <c r="BS2" s="15">
-        <f t="shared" ref="BS2" si="59">BR2+1</f>
         <v>2087</v>
       </c>
       <c r="BT2" s="15">
-        <f t="shared" ref="BT2" si="60">BS2+1</f>
         <v>2088</v>
       </c>
       <c r="BU2" s="15">
-        <f t="shared" ref="BU2" si="61">BT2+1</f>
         <v>2089</v>
       </c>
       <c r="BV2" s="15">
-        <f t="shared" ref="BV2" si="62">BU2+1</f>
         <v>2090</v>
       </c>
       <c r="BW2" s="15">
-        <f t="shared" ref="BW2" si="63">BV2+1</f>
         <v>2091</v>
       </c>
       <c r="BX2" s="15">
-        <f t="shared" ref="BX2" si="64">BW2+1</f>
         <v>2092</v>
       </c>
       <c r="BY2" s="15">
-        <f t="shared" ref="BY2" si="65">BX2+1</f>
         <v>2093</v>
       </c>
       <c r="BZ2" s="15">
-        <f t="shared" ref="BZ2" si="66">BY2+1</f>
         <v>2094</v>
       </c>
       <c r="CA2" s="15">
-        <f t="shared" ref="CA2" si="67">BZ2+1</f>
         <v>2095</v>
       </c>
       <c r="CB2" s="15">
-        <f t="shared" ref="CB2" si="68">CA2+1</f>
         <v>2096</v>
       </c>
     </row>
@@ -3450,6 +3527,46 @@
       <c r="H3" s="1">
         <v>308810</v>
       </c>
+      <c r="I3" s="1">
+        <f>H3*1.11</f>
+        <v>342779.10000000003</v>
+      </c>
+      <c r="J3" s="1">
+        <f>I3*1.1</f>
+        <v>377057.01000000007</v>
+      </c>
+      <c r="K3" s="1">
+        <f>J3*1.09</f>
+        <v>410992.14090000011</v>
+      </c>
+      <c r="L3" s="1">
+        <f>K3*1.08</f>
+        <v>443871.51217200013</v>
+      </c>
+      <c r="M3" s="1">
+        <f>L3*1.07</f>
+        <v>474942.51802404015</v>
+      </c>
+      <c r="N3" s="1">
+        <f>M3*1.06</f>
+        <v>503439.0691054826</v>
+      </c>
+      <c r="O3" s="1">
+        <f>N3*1.05</f>
+        <v>528611.02256075677</v>
+      </c>
+      <c r="P3" s="1">
+        <f>O3*1.04</f>
+        <v>549755.4634631871</v>
+      </c>
+      <c r="Q3" s="1">
+        <f>P3*1.03</f>
+        <v>566248.12736708275</v>
+      </c>
+      <c r="R3" s="1">
+        <f>Q3*1.02</f>
+        <v>577573.08991442446</v>
+      </c>
     </row>
     <row r="4" spans="1:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" t="s">
@@ -3473,6 +3590,46 @@
       <c r="H4" s="1">
         <v>50226</v>
       </c>
+      <c r="I4" s="1">
+        <f>H4*1.25</f>
+        <v>62782.5</v>
+      </c>
+      <c r="J4" s="1">
+        <f>I4*1.15</f>
+        <v>72199.875</v>
+      </c>
+      <c r="K4" s="1">
+        <f>J4*1.05</f>
+        <v>75809.868750000009</v>
+      </c>
+      <c r="L4" s="1">
+        <f>K4*1.1</f>
+        <v>83390.855625000011</v>
+      </c>
+      <c r="M4" s="1">
+        <f>L4*1.1</f>
+        <v>91729.941187500022</v>
+      </c>
+      <c r="N4" s="1">
+        <f>M4*1.07</f>
+        <v>98151.037070625025</v>
+      </c>
+      <c r="O4" s="1">
+        <f>N4*1.08</f>
+        <v>106003.12003627504</v>
+      </c>
+      <c r="P4" s="1">
+        <f>O4*1.09</f>
+        <v>115543.4008395398</v>
+      </c>
+      <c r="Q4" s="1">
+        <f>P4*1.08</f>
+        <v>124786.87290670299</v>
+      </c>
+      <c r="R4" s="1">
+        <f>Q4*1.05</f>
+        <v>131026.21655203815</v>
+      </c>
     </row>
     <row r="5" spans="1:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" t="s">
@@ -3496,6 +3653,46 @@
       <c r="H5" s="1">
         <v>36040</v>
       </c>
+      <c r="I5" s="1">
+        <f>H5*1.1</f>
+        <v>39644</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" ref="J5:R5" si="0">I5*1.1</f>
+        <v>43608.4</v>
+      </c>
+      <c r="K5" s="1">
+        <f t="shared" si="0"/>
+        <v>47969.240000000005</v>
+      </c>
+      <c r="L5" s="1">
+        <f t="shared" si="0"/>
+        <v>52766.164000000012</v>
+      </c>
+      <c r="M5" s="1">
+        <f t="shared" si="0"/>
+        <v>58042.780400000018</v>
+      </c>
+      <c r="N5" s="1">
+        <f t="shared" si="0"/>
+        <v>63847.058440000023</v>
+      </c>
+      <c r="O5" s="1">
+        <f t="shared" si="0"/>
+        <v>70231.764284000034</v>
+      </c>
+      <c r="P5" s="1">
+        <f t="shared" si="0"/>
+        <v>77254.940712400043</v>
+      </c>
+      <c r="Q5" s="1">
+        <f t="shared" si="0"/>
+        <v>84980.434783640056</v>
+      </c>
+      <c r="R5" s="1">
+        <f t="shared" si="0"/>
+        <v>93478.478262004064</v>
+      </c>
     </row>
     <row r="6" spans="1:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" t="s">
@@ -3516,7 +3713,47 @@
       <c r="G6" s="1">
         <v>4089</v>
       </c>
-      <c r="H6" s="59">
+      <c r="H6" s="1">
+        <v>5202</v>
+      </c>
+      <c r="I6" s="1">
+        <f>H6</f>
+        <v>5202</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" ref="J6:R6" si="1">I6</f>
+        <v>5202</v>
+      </c>
+      <c r="K6" s="1">
+        <f t="shared" si="1"/>
+        <v>5202</v>
+      </c>
+      <c r="L6" s="1">
+        <f t="shared" si="1"/>
+        <v>5202</v>
+      </c>
+      <c r="M6" s="1">
+        <f t="shared" si="1"/>
+        <v>5202</v>
+      </c>
+      <c r="N6" s="1">
+        <f t="shared" si="1"/>
+        <v>5202</v>
+      </c>
+      <c r="O6" s="1">
+        <f t="shared" si="1"/>
+        <v>5202</v>
+      </c>
+      <c r="P6" s="1">
+        <f t="shared" si="1"/>
+        <v>5202</v>
+      </c>
+      <c r="Q6" s="1">
+        <f t="shared" si="1"/>
+        <v>5202</v>
+      </c>
+      <c r="R6" s="1">
+        <f t="shared" si="1"/>
         <v>5202</v>
       </c>
     </row>
@@ -3525,28 +3762,68 @@
         <v>4</v>
       </c>
       <c r="C7" s="10">
-        <f>SUM(C3:C6)</f>
+        <f t="shared" ref="C7:H7" si="2">SUM(C3:C6)</f>
         <v>242155</v>
       </c>
       <c r="D7" s="10">
-        <f>SUM(D3:D6)</f>
+        <f t="shared" si="2"/>
         <v>257141</v>
       </c>
       <c r="E7" s="10">
-        <f>SUM(E3:E6)</f>
+        <f t="shared" si="2"/>
         <v>287597</v>
       </c>
       <c r="F7" s="10">
-        <f>SUM(F3:F6)</f>
+        <f t="shared" si="2"/>
         <v>324162</v>
       </c>
       <c r="G7" s="10">
-        <f>SUM(G3:G6)</f>
+        <f t="shared" si="2"/>
         <v>371622</v>
       </c>
       <c r="H7" s="10">
-        <f>SUM(H3:H6)</f>
+        <f t="shared" si="2"/>
         <v>400278</v>
+      </c>
+      <c r="I7" s="10">
+        <f t="shared" ref="I7" si="3">SUM(I3:I6)</f>
+        <v>450407.60000000003</v>
+      </c>
+      <c r="J7" s="10">
+        <f t="shared" ref="J7" si="4">SUM(J3:J6)</f>
+        <v>498067.28500000009</v>
+      </c>
+      <c r="K7" s="10">
+        <f t="shared" ref="K7" si="5">SUM(K3:K6)</f>
+        <v>539973.24965000013</v>
+      </c>
+      <c r="L7" s="10">
+        <f t="shared" ref="L7" si="6">SUM(L3:L6)</f>
+        <v>585230.53179700009</v>
+      </c>
+      <c r="M7" s="10">
+        <f t="shared" ref="M7" si="7">SUM(M3:M6)</f>
+        <v>629917.23961154022</v>
+      </c>
+      <c r="N7" s="10">
+        <f t="shared" ref="N7" si="8">SUM(N3:N6)</f>
+        <v>670639.16461610771</v>
+      </c>
+      <c r="O7" s="10">
+        <f t="shared" ref="O7" si="9">SUM(O3:O6)</f>
+        <v>710047.90688103181</v>
+      </c>
+      <c r="P7" s="10">
+        <f t="shared" ref="P7" si="10">SUM(P3:P6)</f>
+        <v>747755.80501512694</v>
+      </c>
+      <c r="Q7" s="10">
+        <f t="shared" ref="Q7" si="11">SUM(Q3:Q6)</f>
+        <v>781217.43505742587</v>
+      </c>
+      <c r="R7" s="10">
+        <f t="shared" ref="R7" si="12">SUM(R3:R6)</f>
+        <v>807279.78472846665</v>
       </c>
     </row>
     <row r="8" spans="1:80" x14ac:dyDescent="0.55000000000000004">
@@ -3568,8 +3845,48 @@
       <c r="G8" s="1">
         <v>241894</v>
       </c>
-      <c r="H8" s="59">
+      <c r="H8" s="1">
         <v>264185</v>
+      </c>
+      <c r="I8" s="1">
+        <f>I7*0.65</f>
+        <v>292764.94000000006</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" ref="J8:R8" si="13">J7*0.65</f>
+        <v>323743.73525000009</v>
+      </c>
+      <c r="K8" s="1">
+        <f t="shared" si="13"/>
+        <v>350982.61227250012</v>
+      </c>
+      <c r="L8" s="1">
+        <f t="shared" si="13"/>
+        <v>380399.84566805005</v>
+      </c>
+      <c r="M8" s="1">
+        <f t="shared" si="13"/>
+        <v>409446.20574750117</v>
+      </c>
+      <c r="N8" s="1">
+        <f t="shared" si="13"/>
+        <v>435915.45700047002</v>
+      </c>
+      <c r="O8" s="1">
+        <f t="shared" si="13"/>
+        <v>461531.13947267068</v>
+      </c>
+      <c r="P8" s="1">
+        <f t="shared" si="13"/>
+        <v>486041.27325983252</v>
+      </c>
+      <c r="Q8" s="1">
+        <f t="shared" si="13"/>
+        <v>507791.33278732683</v>
+      </c>
+      <c r="R8" s="1">
+        <f t="shared" si="13"/>
+        <v>524731.86007350334</v>
       </c>
     </row>
     <row r="9" spans="1:80" x14ac:dyDescent="0.55000000000000004">
@@ -3591,8 +3908,48 @@
       <c r="G9" s="1">
         <v>54628</v>
       </c>
-      <c r="H9" s="59">
+      <c r="H9" s="1">
         <v>53013</v>
+      </c>
+      <c r="I9" s="1">
+        <f>I7*0.13</f>
+        <v>58552.988000000005</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" ref="J9:R9" si="14">J7*0.13</f>
+        <v>64748.747050000013</v>
+      </c>
+      <c r="K9" s="1">
+        <f t="shared" si="14"/>
+        <v>70196.522454500024</v>
+      </c>
+      <c r="L9" s="1">
+        <f t="shared" si="14"/>
+        <v>76079.969133610008</v>
+      </c>
+      <c r="M9" s="1">
+        <f t="shared" si="14"/>
+        <v>81889.241149500231</v>
+      </c>
+      <c r="N9" s="1">
+        <f t="shared" si="14"/>
+        <v>87183.09140009401</v>
+      </c>
+      <c r="O9" s="1">
+        <f t="shared" si="14"/>
+        <v>92306.227894534139</v>
+      </c>
+      <c r="P9" s="1">
+        <f t="shared" si="14"/>
+        <v>97208.254651966505</v>
+      </c>
+      <c r="Q9" s="1">
+        <f t="shared" si="14"/>
+        <v>101558.26655746537</v>
+      </c>
+      <c r="R9" s="1">
+        <f t="shared" si="14"/>
+        <v>104946.37201470067</v>
       </c>
     </row>
     <row r="10" spans="1:80" x14ac:dyDescent="0.55000000000000004">
@@ -3614,8 +3971,48 @@
       <c r="G10" s="1">
         <v>38770</v>
       </c>
-      <c r="H10" s="59">
+      <c r="H10" s="1">
         <v>46694</v>
+      </c>
+      <c r="I10" s="1">
+        <f>I7*0.116</f>
+        <v>52247.281600000009</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" ref="J10:R10" si="15">J7*0.116</f>
+        <v>57775.805060000013</v>
+      </c>
+      <c r="K10" s="1">
+        <f t="shared" si="15"/>
+        <v>62636.896959400015</v>
+      </c>
+      <c r="L10" s="1">
+        <f t="shared" si="15"/>
+        <v>67886.741688452021</v>
+      </c>
+      <c r="M10" s="1">
+        <f t="shared" si="15"/>
+        <v>73070.399794938668</v>
+      </c>
+      <c r="N10" s="1">
+        <f t="shared" si="15"/>
+        <v>77794.143095468491</v>
+      </c>
+      <c r="O10" s="1">
+        <f t="shared" si="15"/>
+        <v>82365.557198199691</v>
+      </c>
+      <c r="P10" s="1">
+        <f t="shared" si="15"/>
+        <v>86739.673381754736</v>
+      </c>
+      <c r="Q10" s="1">
+        <f t="shared" si="15"/>
+        <v>90621.222466661406</v>
+      </c>
+      <c r="R10" s="1">
+        <f t="shared" si="15"/>
+        <v>93644.45502850214</v>
       </c>
     </row>
     <row r="11" spans="1:80" x14ac:dyDescent="0.55000000000000004">
@@ -3637,8 +4034,48 @@
       <c r="G11" s="1">
         <v>3972</v>
       </c>
-      <c r="H11" s="59">
+      <c r="H11" s="1">
         <v>4099</v>
+      </c>
+      <c r="I11" s="1">
+        <f>H11*1.0864</f>
+        <v>4453.1536000000006</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" ref="J11:R11" si="16">I11*1.0864</f>
+        <v>4837.9060710400008</v>
+      </c>
+      <c r="K11" s="1">
+        <f t="shared" si="16"/>
+        <v>5255.901155577857</v>
+      </c>
+      <c r="L11" s="1">
+        <f t="shared" si="16"/>
+        <v>5710.0110154197837</v>
+      </c>
+      <c r="M11" s="1">
+        <f t="shared" si="16"/>
+        <v>6203.3559671520534</v>
+      </c>
+      <c r="N11" s="1">
+        <f t="shared" si="16"/>
+        <v>6739.3259227139906</v>
+      </c>
+      <c r="O11" s="1">
+        <f t="shared" si="16"/>
+        <v>7321.6036824364792</v>
+      </c>
+      <c r="P11" s="1">
+        <f t="shared" si="16"/>
+        <v>7954.1902405989913</v>
+      </c>
+      <c r="Q11" s="1">
+        <f t="shared" si="16"/>
+        <v>8641.4322773867443</v>
+      </c>
+      <c r="R11" s="1">
+        <f t="shared" si="16"/>
+        <v>9388.05202615296</v>
       </c>
     </row>
     <row r="12" spans="1:80" x14ac:dyDescent="0.55000000000000004">
@@ -3646,28 +4083,68 @@
         <v>9</v>
       </c>
       <c r="C12" s="10">
-        <f>SUM(C8:C11)</f>
+        <f t="shared" ref="C12:H12" si="17">SUM(C8:C11)</f>
         <v>222470</v>
       </c>
       <c r="D12" s="10">
-        <f>SUM(D8:D11)</f>
+        <f t="shared" si="17"/>
         <v>234736</v>
       </c>
       <c r="E12" s="10">
-        <f t="shared" ref="E12:G12" si="69">SUM(E8:E11)</f>
+        <f t="shared" si="17"/>
         <v>263627</v>
       </c>
       <c r="F12" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="17"/>
         <v>295727</v>
       </c>
       <c r="G12" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="17"/>
         <v>339264</v>
       </c>
       <c r="H12" s="10">
-        <f t="shared" ref="H12" si="70">SUM(H8:H11)</f>
+        <f t="shared" si="17"/>
         <v>367991</v>
+      </c>
+      <c r="I12" s="10">
+        <f t="shared" ref="I12" si="18">SUM(I8:I11)</f>
+        <v>408018.36320000008</v>
+      </c>
+      <c r="J12" s="10">
+        <f t="shared" ref="J12" si="19">SUM(J8:J11)</f>
+        <v>451106.1934310401</v>
+      </c>
+      <c r="K12" s="10">
+        <f t="shared" ref="K12" si="20">SUM(K8:K11)</f>
+        <v>489071.93284197804</v>
+      </c>
+      <c r="L12" s="10">
+        <f t="shared" ref="L12" si="21">SUM(L8:L11)</f>
+        <v>530076.56750553183</v>
+      </c>
+      <c r="M12" s="10">
+        <f t="shared" ref="M12" si="22">SUM(M8:M11)</f>
+        <v>570609.20265909215</v>
+      </c>
+      <c r="N12" s="10">
+        <f t="shared" ref="N12" si="23">SUM(N8:N11)</f>
+        <v>607632.01741874649</v>
+      </c>
+      <c r="O12" s="10">
+        <f t="shared" ref="O12" si="24">SUM(O8:O11)</f>
+        <v>643524.52824784105</v>
+      </c>
+      <c r="P12" s="10">
+        <f t="shared" ref="P12" si="25">SUM(P8:P11)</f>
+        <v>677943.39153415279</v>
+      </c>
+      <c r="Q12" s="10">
+        <f t="shared" ref="Q12" si="26">SUM(Q8:Q11)</f>
+        <v>708612.25408884033</v>
+      </c>
+      <c r="R12" s="10">
+        <f t="shared" ref="R12" si="27">SUM(R8:R11)</f>
+        <v>732710.73914285912</v>
       </c>
     </row>
     <row r="13" spans="1:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
@@ -3675,28 +4152,68 @@
         <v>10</v>
       </c>
       <c r="C13" s="11">
-        <f>C7-C8-C9-C10-C11</f>
+        <f t="shared" ref="C13:H13" si="28">C7-C8-C9-C10-C11</f>
         <v>19685</v>
       </c>
       <c r="D13" s="11">
-        <f>D7-D8-D9-D10-D11</f>
+        <f t="shared" si="28"/>
         <v>22405</v>
       </c>
       <c r="E13" s="11">
-        <f>E7-E8-E9-E10-E11</f>
+        <f t="shared" si="28"/>
         <v>23970</v>
       </c>
       <c r="F13" s="11">
-        <f>F7-F8-F9-F10-F11</f>
+        <f t="shared" si="28"/>
         <v>28435</v>
       </c>
       <c r="G13" s="11">
-        <f>G7-G8-G9-G10-G11</f>
+        <f t="shared" si="28"/>
         <v>32358</v>
       </c>
       <c r="H13" s="11">
-        <f>H7-H8-H9-H10-H11</f>
+        <f t="shared" si="28"/>
         <v>32287</v>
+      </c>
+      <c r="I13" s="11">
+        <f t="shared" ref="I13:R13" si="29">I7-I8-I9-I10-I11</f>
+        <v>42389.236799999955</v>
+      </c>
+      <c r="J13" s="11">
+        <f t="shared" si="29"/>
+        <v>46961.091568959986</v>
+      </c>
+      <c r="K13" s="11">
+        <f t="shared" si="29"/>
+        <v>50901.316808022115</v>
+      </c>
+      <c r="L13" s="11">
+        <f t="shared" si="29"/>
+        <v>55153.964291468226</v>
+      </c>
+      <c r="M13" s="11">
+        <f t="shared" si="29"/>
+        <v>59308.036952448085</v>
+      </c>
+      <c r="N13" s="11">
+        <f t="shared" si="29"/>
+        <v>63007.147197361192</v>
+      </c>
+      <c r="O13" s="11">
+        <f t="shared" si="29"/>
+        <v>66523.378633190834</v>
+      </c>
+      <c r="P13" s="11">
+        <f t="shared" si="29"/>
+        <v>69812.413480974181</v>
+      </c>
+      <c r="Q13" s="11">
+        <f t="shared" si="29"/>
+        <v>72605.180968585526</v>
+      </c>
+      <c r="R13" s="11">
+        <f t="shared" si="29"/>
+        <v>74569.045585607542</v>
       </c>
     </row>
     <row r="14" spans="1:80" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004">
@@ -3718,8 +4235,48 @@
       <c r="G14" s="1">
         <v>-3246</v>
       </c>
-      <c r="H14" s="59">
+      <c r="H14" s="1">
         <v>-3906</v>
+      </c>
+      <c r="I14" s="1">
+        <f>H14*1.06</f>
+        <v>-4140.3600000000006</v>
+      </c>
+      <c r="J14" s="1">
+        <f>I14*1.14</f>
+        <v>-4720.0104000000001</v>
+      </c>
+      <c r="K14" s="1">
+        <f>J14*1.03</f>
+        <v>-4861.6107120000006</v>
+      </c>
+      <c r="L14" s="1">
+        <f>K14*1.2</f>
+        <v>-5833.9328544000009</v>
+      </c>
+      <c r="M14" s="1">
+        <f>L14*1.19</f>
+        <v>-6942.3800967360012</v>
+      </c>
+      <c r="N14" s="1">
+        <f>M14*1.12</f>
+        <v>-7775.4657083443217</v>
+      </c>
+      <c r="O14" s="1">
+        <f>N14*0.99</f>
+        <v>-7697.7110512608788</v>
+      </c>
+      <c r="P14" s="1">
+        <f>O14*1.09</f>
+        <v>-8390.505045874359</v>
+      </c>
+      <c r="Q14" s="1">
+        <f>P14*0.8</f>
+        <v>-6712.4040366994877</v>
+      </c>
+      <c r="R14" s="1">
+        <f>Q14*0.88</f>
+        <v>-5906.9155522955489</v>
       </c>
     </row>
     <row r="15" spans="1:80" x14ac:dyDescent="0.55000000000000004">
@@ -3731,9 +4288,19 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="59">
+      <c r="H15" s="1">
         <v>-8310</v>
       </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
     </row>
     <row r="16" spans="1:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" t="s">
@@ -3754,422 +4321,446 @@
       <c r="G16" s="1">
         <v>-5968</v>
       </c>
-      <c r="H16" s="59">
+      <c r="H16" s="1">
         <v>-4829</v>
       </c>
-      <c r="N16" s="54"/>
-      <c r="O16" s="54"/>
-      <c r="P16" s="54"/>
-      <c r="Q16" s="54"/>
-      <c r="R16" s="54"/>
-      <c r="S16" s="54"/>
-      <c r="T16" s="54"/>
-      <c r="U16" s="54"/>
-      <c r="V16" s="54"/>
-      <c r="W16" s="54"/>
-      <c r="X16" s="54"/>
-      <c r="Y16" s="54"/>
-      <c r="Z16" s="54"/>
-      <c r="AA16" s="54"/>
+      <c r="I16" s="1">
+        <f>(I13+I14)*-0.207457</f>
+        <v>-7934.9972342975907</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" ref="J16:R16" si="30">(J13+J14)*-0.207457</f>
+        <v>-8763.2079760689321</v>
+      </c>
+      <c r="K16" s="1">
+        <f t="shared" si="30"/>
+        <v>-9551.2593075624591</v>
+      </c>
+      <c r="L16" s="1">
+        <f t="shared" si="30"/>
+        <v>-10231.785761839863</v>
+      </c>
+      <c r="M16" s="1">
+        <f t="shared" si="30"/>
+        <v>-10863.622074315463</v>
+      </c>
+      <c r="N16" s="1">
+        <f t="shared" si="30"/>
+        <v>-11458.198946666973</v>
+      </c>
+      <c r="O16" s="1">
+        <f t="shared" si="30"/>
+        <v>-12203.796519544443</v>
+      </c>
+      <c r="P16" s="1">
+        <f t="shared" si="30"/>
+        <v>-12742.404858220505</v>
+      </c>
+      <c r="Q16" s="1">
+        <f t="shared" si="30"/>
+        <v>-13669.917823958282</v>
+      </c>
+      <c r="R16" s="1">
+        <f t="shared" si="30"/>
+        <v>-14244.439510320804</v>
+      </c>
+      <c r="S16" s="62"/>
+      <c r="T16" s="62"/>
+      <c r="U16" s="62"/>
+      <c r="V16" s="62"/>
+      <c r="W16" s="62"/>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="62"/>
+      <c r="Z16" s="62"/>
+      <c r="AA16" s="62"/>
     </row>
     <row r="17" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B17" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="11">
-        <f>SUM(C13:C16)</f>
+        <f t="shared" ref="C17:H17" si="31">SUM(C13:C16)</f>
         <v>14239</v>
       </c>
       <c r="D17" s="11">
-        <f>SUM(D13:D16)</f>
+        <f t="shared" si="31"/>
         <v>15769</v>
       </c>
       <c r="E17" s="11">
-        <f>SUM(E13:E16)</f>
+        <f t="shared" si="31"/>
         <v>17732</v>
       </c>
       <c r="F17" s="11">
-        <f>SUM(F13:F16)</f>
+        <f t="shared" si="31"/>
         <v>20639</v>
       </c>
       <c r="G17" s="11">
-        <f>SUM(G13:G16)</f>
+        <f t="shared" si="31"/>
         <v>23144</v>
       </c>
       <c r="H17" s="11">
-        <f>SUM(H13:H16)</f>
+        <f t="shared" si="31"/>
         <v>15242</v>
       </c>
-      <c r="I17" s="55">
-        <f>H17*$I$21</f>
-        <v>16766.2</v>
-      </c>
-      <c r="J17" s="55">
-        <f t="shared" ref="J17:R17" si="71">I17*$I$21</f>
-        <v>18442.820000000003</v>
-      </c>
-      <c r="K17" s="55">
-        <f t="shared" si="71"/>
-        <v>20287.102000000006</v>
-      </c>
-      <c r="L17" s="55">
-        <f t="shared" si="71"/>
-        <v>22315.812200000008</v>
-      </c>
-      <c r="M17" s="55">
-        <f t="shared" si="71"/>
-        <v>24547.393420000011</v>
-      </c>
-      <c r="N17" s="55">
-        <f t="shared" si="71"/>
-        <v>27002.132762000016</v>
-      </c>
-      <c r="O17" s="55">
-        <f t="shared" si="71"/>
-        <v>29702.346038200019</v>
-      </c>
-      <c r="P17" s="55">
-        <f t="shared" si="71"/>
-        <v>32672.580642020024</v>
-      </c>
-      <c r="Q17" s="55">
-        <f t="shared" si="71"/>
-        <v>35939.838706222028</v>
-      </c>
-      <c r="R17" s="55">
-        <f t="shared" si="71"/>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="S17" s="55">
-        <f t="shared" ref="S17:V17" si="72">R17*$R$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="T17" s="55">
-        <f t="shared" si="72"/>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="U17" s="55">
-        <f t="shared" si="72"/>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="V17" s="55">
-        <f t="shared" si="72"/>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="W17" s="55">
-        <f>V17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="X17" s="55">
-        <f t="shared" ref="X17:AA17" si="73">W17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="Y17" s="55">
-        <f t="shared" si="73"/>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="Z17" s="55">
-        <f t="shared" si="73"/>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AA17" s="55">
-        <f t="shared" si="73"/>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AB17" s="55">
-        <f t="shared" ref="AB17" si="74">AA17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AC17" s="55">
-        <f t="shared" ref="AC17" si="75">AB17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AD17" s="55">
-        <f t="shared" ref="AD17" si="76">AC17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AE17" s="55">
-        <f t="shared" ref="AE17" si="77">AD17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AF17" s="55">
-        <f t="shared" ref="AF17" si="78">AE17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AG17" s="55">
-        <f t="shared" ref="AG17" si="79">AF17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AH17" s="55">
-        <f t="shared" ref="AH17" si="80">AG17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AI17" s="55">
-        <f t="shared" ref="AI17" si="81">AH17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AJ17" s="55">
-        <f t="shared" ref="AJ17" si="82">AI17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AK17" s="55">
-        <f t="shared" ref="AK17" si="83">AJ17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AL17" s="55">
-        <f t="shared" ref="AL17" si="84">AK17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AM17" s="55">
-        <f t="shared" ref="AM17" si="85">AL17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AN17" s="55">
-        <f t="shared" ref="AN17" si="86">AM17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AO17" s="55">
-        <f t="shared" ref="AO17" si="87">AN17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AP17" s="55">
-        <f t="shared" ref="AP17" si="88">AO17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AQ17" s="55">
-        <f t="shared" ref="AQ17" si="89">AP17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AR17" s="55">
-        <f t="shared" ref="AR17" si="90">AQ17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AS17" s="55">
-        <f t="shared" ref="AS17" si="91">AR17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AT17" s="55">
-        <f t="shared" ref="AT17" si="92">AS17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AU17" s="55">
-        <f t="shared" ref="AU17" si="93">AT17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AV17" s="55">
-        <f t="shared" ref="AV17" si="94">AU17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AW17" s="55">
-        <f t="shared" ref="AW17" si="95">AV17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AX17" s="55">
-        <f t="shared" ref="AX17" si="96">AW17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AY17" s="55">
-        <f t="shared" ref="AY17" si="97">AX17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="AZ17" s="55">
-        <f t="shared" ref="AZ17" si="98">AY17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BA17" s="55">
-        <f t="shared" ref="BA17" si="99">AZ17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BB17" s="55">
-        <f t="shared" ref="BB17" si="100">BA17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BC17" s="55">
-        <f t="shared" ref="BC17" si="101">BB17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BD17" s="55">
-        <f t="shared" ref="BD17" si="102">BC17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BE17" s="55">
-        <f t="shared" ref="BE17" si="103">BD17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BF17" s="55">
-        <f t="shared" ref="BF17" si="104">BE17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BG17" s="55">
-        <f t="shared" ref="BG17" si="105">BF17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BH17" s="55">
-        <f t="shared" ref="BH17" si="106">BG17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BI17" s="55">
-        <f t="shared" ref="BI17" si="107">BH17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BJ17" s="55">
-        <f t="shared" ref="BJ17" si="108">BI17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BK17" s="55">
-        <f t="shared" ref="BK17" si="109">BJ17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BL17" s="55">
-        <f t="shared" ref="BL17" si="110">BK17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BM17" s="55">
-        <f t="shared" ref="BM17" si="111">BL17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BN17" s="55">
-        <f t="shared" ref="BN17" si="112">BM17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BO17" s="55">
-        <f t="shared" ref="BO17" si="113">BN17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BP17" s="55">
-        <f t="shared" ref="BP17" si="114">BO17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BQ17" s="55">
-        <f t="shared" ref="BQ17" si="115">BP17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BR17" s="55">
-        <f t="shared" ref="BR17" si="116">BQ17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BS17" s="55">
-        <f t="shared" ref="BS17" si="117">BR17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BT17" s="55">
-        <f t="shared" ref="BT17" si="118">BS17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BU17" s="55">
-        <f t="shared" ref="BU17" si="119">BT17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BV17" s="55">
-        <f t="shared" ref="BV17" si="120">BU17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BW17" s="55">
-        <f t="shared" ref="BW17" si="121">BV17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BX17" s="55">
-        <f t="shared" ref="BX17" si="122">BW17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BY17" s="55">
-        <f t="shared" ref="BY17" si="123">BX17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="BZ17" s="55">
-        <f t="shared" ref="BZ17" si="124">BY17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="CA17" s="55">
-        <f t="shared" ref="CA17" si="125">BZ17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-      <c r="CB17" s="55">
-        <f t="shared" ref="CB17" si="126">CA17*$W$21</f>
-        <v>39533.822576844235</v>
-      </c>
-    </row>
-    <row r="18" spans="2:80" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.6"/>
+      <c r="I17" s="11">
+        <f t="shared" ref="I17" si="32">SUM(I13:I16)</f>
+        <v>30313.879565702366</v>
+      </c>
+      <c r="J17" s="11">
+        <f t="shared" ref="J17" si="33">SUM(J13:J16)</f>
+        <v>33477.873192891057</v>
+      </c>
+      <c r="K17" s="11">
+        <f t="shared" ref="K17" si="34">SUM(K13:K16)</f>
+        <v>36488.446788459652</v>
+      </c>
+      <c r="L17" s="11">
+        <f t="shared" ref="L17" si="35">SUM(L13:L16)</f>
+        <v>39088.245675228362</v>
+      </c>
+      <c r="M17" s="11">
+        <f t="shared" ref="M17" si="36">SUM(M13:M16)</f>
+        <v>41502.034781396622</v>
+      </c>
+      <c r="N17" s="11">
+        <f t="shared" ref="N17" si="37">SUM(N13:N16)</f>
+        <v>43773.482542349899</v>
+      </c>
+      <c r="O17" s="11">
+        <f t="shared" ref="O17" si="38">SUM(O13:O16)</f>
+        <v>46621.871062385515</v>
+      </c>
+      <c r="P17" s="11">
+        <f t="shared" ref="P17" si="39">SUM(P13:P16)</f>
+        <v>48679.503576879317</v>
+      </c>
+      <c r="Q17" s="11">
+        <f t="shared" ref="Q17" si="40">SUM(Q13:Q16)</f>
+        <v>52222.859107927754</v>
+      </c>
+      <c r="R17" s="11">
+        <f t="shared" ref="R17" si="41">SUM(R13:R16)</f>
+        <v>54417.690522991179</v>
+      </c>
+      <c r="S17" s="53">
+        <f>R17*(1+$T$21)</f>
+        <v>54961.867428221092</v>
+      </c>
+      <c r="T17" s="53">
+        <f>S17*(1+$T$21)</f>
+        <v>55511.486102503302</v>
+      </c>
+      <c r="U17" s="53">
+        <f>T17*(1+$T$21)</f>
+        <v>56066.600963528334</v>
+      </c>
+      <c r="V17" s="53">
+        <f>U17*(1+$T$21)</f>
+        <v>56627.26697316362</v>
+      </c>
+      <c r="W17" s="53">
+        <f>V17*(1+$T$21)</f>
+        <v>57193.539642895259</v>
+      </c>
+      <c r="X17" s="53">
+        <f>W17*(1+$T$21)</f>
+        <v>57765.475039324214</v>
+      </c>
+      <c r="Y17" s="53">
+        <f>X17*(1+$T$21)</f>
+        <v>58343.129789717459</v>
+      </c>
+      <c r="Z17" s="53">
+        <f>Y17*(1+$T$21)</f>
+        <v>58926.561087614631</v>
+      </c>
+      <c r="AA17" s="53">
+        <f>Z17*(1+$T$21)</f>
+        <v>59515.826698490775</v>
+      </c>
+      <c r="AB17" s="53">
+        <f>AA17*(1+$T$21)</f>
+        <v>60110.984965475684</v>
+      </c>
+      <c r="AC17" s="53">
+        <f>AB17*(1+$T$21)</f>
+        <v>60712.09481513044</v>
+      </c>
+      <c r="AD17" s="53">
+        <f>AC17*(1+$T$21)</f>
+        <v>61319.215763281747</v>
+      </c>
+      <c r="AE17" s="53">
+        <f>AD17*(1+$T$21)</f>
+        <v>61932.407920914564</v>
+      </c>
+      <c r="AF17" s="53">
+        <f>AE17*(1+$T$21)</f>
+        <v>62551.732000123709</v>
+      </c>
+      <c r="AG17" s="53">
+        <f>AF17*(1+$T$21)</f>
+        <v>63177.249320124945</v>
+      </c>
+      <c r="AH17" s="53">
+        <f>AG17*(1+$T$21)</f>
+        <v>63809.021813326195</v>
+      </c>
+      <c r="AI17" s="53">
+        <f>AH17*(1+$T$21)</f>
+        <v>64447.112031459459</v>
+      </c>
+      <c r="AJ17" s="53">
+        <f>AI17*(1+$T$21)</f>
+        <v>65091.583151774052</v>
+      </c>
+      <c r="AK17" s="53">
+        <f>AJ17*(1+$T$21)</f>
+        <v>65742.498983291793</v>
+      </c>
+      <c r="AL17" s="53">
+        <f>AK17*(1+$T$21)</f>
+        <v>66399.923973124707</v>
+      </c>
+      <c r="AM17" s="53">
+        <f>AL17*(1+$T$21)</f>
+        <v>67063.923212855952</v>
+      </c>
+      <c r="AN17" s="53">
+        <f>AM17*(1+$T$21)</f>
+        <v>67734.562444984505</v>
+      </c>
+      <c r="AO17" s="53">
+        <f>AN17*(1+$T$21)</f>
+        <v>68411.908069434357</v>
+      </c>
+      <c r="AP17" s="53">
+        <f>AO17*(1+$T$21)</f>
+        <v>69096.027150128706</v>
+      </c>
+      <c r="AQ17" s="53">
+        <f>AP17*(1+$T$21)</f>
+        <v>69786.987421629994</v>
+      </c>
+      <c r="AR17" s="53">
+        <f>AQ17*(1+$T$21)</f>
+        <v>70484.85729584629</v>
+      </c>
+      <c r="AS17" s="53">
+        <f>AR17*(1+$T$21)</f>
+        <v>71189.705868804755</v>
+      </c>
+      <c r="AT17" s="53">
+        <f>AS17*(1+$T$21)</f>
+        <v>71901.602927492801</v>
+      </c>
+      <c r="AU17" s="53">
+        <f>AT17*(1+$T$21)</f>
+        <v>72620.618956767736</v>
+      </c>
+      <c r="AV17" s="53">
+        <f>AU17*(1+$T$21)</f>
+        <v>73346.82514633541</v>
+      </c>
+      <c r="AW17" s="53">
+        <f>AV17*(1+$T$21)</f>
+        <v>74080.29339779877</v>
+      </c>
+      <c r="AX17" s="53">
+        <f>AW17*(1+$T$21)</f>
+        <v>74821.09633177676</v>
+      </c>
+      <c r="AY17" s="53">
+        <f>AX17*(1+$T$21)</f>
+        <v>75569.307295094535</v>
+      </c>
+      <c r="AZ17" s="53">
+        <f>AY17*(1+$T$21)</f>
+        <v>76325.000368045483</v>
+      </c>
+      <c r="BA17" s="53">
+        <f>AZ17*(1+$T$21)</f>
+        <v>77088.250371725939</v>
+      </c>
+      <c r="BB17" s="53">
+        <f>BA17*(1+$T$21)</f>
+        <v>77859.132875443203</v>
+      </c>
+      <c r="BC17" s="53">
+        <f>BB17*(1+$T$21)</f>
+        <v>78637.724204197642</v>
+      </c>
+      <c r="BD17" s="53">
+        <f>BC17*(1+$T$21)</f>
+        <v>79424.101446239612</v>
+      </c>
+      <c r="BE17" s="53">
+        <f>BD17*(1+$T$21)</f>
+        <v>80218.342460702013</v>
+      </c>
+      <c r="BF17" s="53">
+        <f>BE17*(1+$T$21)</f>
+        <v>81020.525885309034</v>
+      </c>
+      <c r="BG17" s="53">
+        <f>BF17*(1+$T$21)</f>
+        <v>81830.731144162128</v>
+      </c>
+      <c r="BH17" s="53">
+        <f>BG17*(1+$T$21)</f>
+        <v>82649.038455603746</v>
+      </c>
+      <c r="BI17" s="53">
+        <f>BH17*(1+$T$21)</f>
+        <v>83475.528840159779</v>
+      </c>
+      <c r="BJ17" s="53">
+        <f>BI17*(1+$T$21)</f>
+        <v>84310.284128561383</v>
+      </c>
+      <c r="BK17" s="53">
+        <f>BJ17*(1+$T$21)</f>
+        <v>85153.386969846993</v>
+      </c>
+      <c r="BL17" s="53">
+        <f>BK17*(1+$T$21)</f>
+        <v>86004.920839545463</v>
+      </c>
+      <c r="BM17" s="53">
+        <f>BL17*(1+$T$21)</f>
+        <v>86864.970047940922</v>
+      </c>
+      <c r="BN17" s="53">
+        <f>BM17*(1+$T$21)</f>
+        <v>87733.619748420329</v>
+      </c>
+      <c r="BO17" s="53">
+        <f>BN17*(1+$T$21)</f>
+        <v>88610.955945904527</v>
+      </c>
+      <c r="BP17" s="53">
+        <f>BO17*(1+$T$21)</f>
+        <v>89497.065505363571</v>
+      </c>
+      <c r="BQ17" s="53">
+        <f>BP17*(1+$T$21)</f>
+        <v>90392.036160417207</v>
+      </c>
+      <c r="BR17" s="53">
+        <f>BQ17*(1+$T$21)</f>
+        <v>91295.956522021384</v>
+      </c>
+      <c r="BS17" s="53">
+        <f>BR17*(1+$T$21)</f>
+        <v>92208.916087241596</v>
+      </c>
+      <c r="BT17" s="53">
+        <f>BS17*(1+$T$21)</f>
+        <v>93131.005248114016</v>
+      </c>
+      <c r="BU17" s="53">
+        <f>BT17*(1+$T$21)</f>
+        <v>94062.315300595161</v>
+      </c>
+      <c r="BV17" s="53">
+        <f>BU17*(1+$T$21)</f>
+        <v>95002.93845360112</v>
+      </c>
+      <c r="BW17" s="53">
+        <f>BV17*(1+$T$21)</f>
+        <v>95952.967838137134</v>
+      </c>
+      <c r="BX17" s="53">
+        <f>BW17*(1+$T$21)</f>
+        <v>96912.497516518502</v>
+      </c>
+      <c r="BY17" s="53">
+        <f>BX17*(1+$T$21)</f>
+        <v>97881.622491683695</v>
+      </c>
+      <c r="BZ17" s="53">
+        <f>BY17*(1+$T$21)</f>
+        <v>98860.438716600533</v>
+      </c>
+      <c r="CA17" s="53">
+        <f>BZ17*(1+$T$21)</f>
+        <v>99849.04310376654</v>
+      </c>
+      <c r="CB17" s="53">
+        <f>CA17*(1+$T$21)</f>
+        <v>100847.53353480421</v>
+      </c>
+    </row>
+    <row r="18" spans="2:80" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="19" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="O19" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="P19" s="26"/>
-    </row>
-    <row r="20" spans="2:80" x14ac:dyDescent="0.55000000000000004">
-      <c r="H20" s="41"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="J20" s="41"/>
       <c r="K20" s="41"/>
       <c r="L20" s="41"/>
       <c r="M20" s="41"/>
-      <c r="O20" s="50" t="s">
+      <c r="S20" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="T20" s="26"/>
+    </row>
+    <row r="21" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="I21" s="42"/>
+      <c r="S21" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="P20" s="51">
+      <c r="T21" s="50">
         <v>0.01</v>
       </c>
     </row>
-    <row r="21" spans="2:80" x14ac:dyDescent="0.55000000000000004">
-      <c r="I21" s="42">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="O21" s="34" t="s">
+    <row r="22" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="S22" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="P21" s="52">
+      <c r="T22" s="51">
         <v>7.8200000000000006E-2</v>
       </c>
-      <c r="R21">
-        <v>1</v>
-      </c>
-      <c r="W21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="O22" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="P22" s="66">
-        <f>NPV(P21,H17:CV17)</f>
-        <v>390977.59268140903</v>
-      </c>
-      <c r="W22" s="49"/>
-    </row>
-    <row r="23" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="23" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B23" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="8">
-        <f>C13/C7</f>
+        <f t="shared" ref="C23:H23" si="42">C13/C7</f>
         <v>8.1290908715492147E-2</v>
       </c>
       <c r="D23" s="8">
-        <f>D13/D7</f>
+        <f t="shared" si="42"/>
         <v>8.7131184836334932E-2</v>
       </c>
       <c r="E23" s="8">
-        <f>E13/E7</f>
+        <f t="shared" si="42"/>
         <v>8.3345792897700596E-2</v>
       </c>
       <c r="F23" s="8">
-        <f>F13/F7</f>
+        <f t="shared" si="42"/>
         <v>8.7718486435794454E-2</v>
       </c>
       <c r="G23" s="8">
-        <f>G13/G7</f>
+        <f t="shared" si="42"/>
         <v>8.7072347708155057E-2</v>
       </c>
       <c r="H23" s="8">
-        <f>H13/H7</f>
+        <f t="shared" si="42"/>
         <v>8.0661440298992207E-2</v>
       </c>
-      <c r="O23" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="P23" s="67">
-        <f>P22/EV!E6</f>
-        <v>431.69815820928301</v>
+      <c r="S23" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="T23" s="59">
+        <f>NPV(T22,H17:CV17)</f>
+        <v>617527.17800957547</v>
       </c>
     </row>
     <row r="24" spans="2:80" x14ac:dyDescent="0.55000000000000004">
@@ -4177,38 +4768,38 @@
         <v>16</v>
       </c>
       <c r="C24" s="8">
-        <f>C17/C7</f>
+        <f t="shared" ref="C24:H24" si="43">C17/C7</f>
         <v>5.8801181061716667E-2</v>
       </c>
       <c r="D24" s="8">
-        <f>D17/D7</f>
+        <f t="shared" si="43"/>
         <v>6.1324331786840686E-2</v>
       </c>
       <c r="E24" s="8">
-        <f>E17/E7</f>
+        <f t="shared" si="43"/>
         <v>6.1655719635462125E-2</v>
       </c>
       <c r="F24" s="8">
-        <f>F17/F7</f>
+        <f t="shared" si="43"/>
         <v>6.3668782892504369E-2</v>
       </c>
       <c r="G24" s="8">
-        <f>G17/G7</f>
+        <f t="shared" si="43"/>
         <v>6.2278336589330019E-2</v>
       </c>
       <c r="H24" s="8">
-        <f>H17/H7</f>
+        <f t="shared" si="43"/>
         <v>3.8078535417884571E-2</v>
       </c>
-      <c r="O24" s="64" t="s">
-        <v>49</v>
-      </c>
-      <c r="P24" s="68">
-        <f>EV!E5</f>
-        <v>309.87</v>
-      </c>
-    </row>
-    <row r="25" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="S24" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="T24" s="60">
+        <f>T23/EV!E6</f>
+        <v>681.84302727583372</v>
+      </c>
+    </row>
+    <row r="25" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" t="s">
         <v>23</v>
       </c>
@@ -4233,15 +4824,14 @@
         <f>H7/G7-1</f>
         <v>7.7110612396467326E-2</v>
       </c>
-      <c r="O25" s="69" t="s">
-        <v>50</v>
-      </c>
-      <c r="P25" s="53">
-        <f>P23-P24</f>
-        <v>121.828158209283</v>
-      </c>
-    </row>
-    <row r="26" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="S25" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="T25" s="61">
+        <v>359.66</v>
+      </c>
+    </row>
+    <row r="26" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B26" t="s">
         <v>24</v>
       </c>
@@ -4266,8 +4856,38 @@
         <f>H12/G12-1</f>
         <v>8.4674471797774098E-2</v>
       </c>
-    </row>
-    <row r="28" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
+      <c r="S26" s="33" t="str">
+        <f>IF(T26&gt;=0,"Underpriced","Overpriced")</f>
+        <v>Underpriced</v>
+      </c>
+      <c r="T26" s="52">
+        <f>T24-T25</f>
+        <v>322.18302727583369</v>
+      </c>
+    </row>
+    <row r="27" spans="2:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="D27" s="8">
+        <f>(D17/C17)-1</f>
+        <v>0.10745136596671112</v>
+      </c>
+      <c r="E27" s="8">
+        <f t="shared" ref="E27:H27" si="44">(E17/D17)-1</f>
+        <v>0.12448474855729597</v>
+      </c>
+      <c r="F27" s="8">
+        <f t="shared" si="44"/>
+        <v>0.16394089781186549</v>
+      </c>
+      <c r="G27" s="8">
+        <f t="shared" si="44"/>
+        <v>0.12137215950385194</v>
+      </c>
+      <c r="H27" s="8">
+        <f t="shared" si="44"/>
+        <v>-0.34142758382302107</v>
+      </c>
+    </row>
+    <row r="28" spans="2:80" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="29" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B29" s="43" t="s">
         <v>40</v>
@@ -4281,356 +4901,420 @@
       <c r="I29" s="20" t="s">
         <v>44</v>
       </c>
+      <c r="S29" s="67" t="s">
+        <v>50</v>
+      </c>
+      <c r="T29" s="68"/>
+      <c r="U29" s="68"/>
+      <c r="V29" s="68"/>
+      <c r="W29" s="68"/>
+      <c r="X29" s="68"/>
+      <c r="Y29" s="69"/>
     </row>
     <row r="30" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="34" t="s">
         <v>0</v>
       </c>
       <c r="D30" s="41">
-        <f t="shared" ref="D30:H41" si="127">D3/C3-1</f>
+        <f t="shared" ref="D30:H41" si="45">D3/C3-1</f>
         <v>6.2093105393280945E-2</v>
       </c>
       <c r="E30" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.12286701277558842</v>
       </c>
       <c r="F30" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.13669093368341478</v>
       </c>
       <c r="G30" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.13093168764606844</v>
       </c>
       <c r="H30" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>6.1834011285059498E-2</v>
       </c>
       <c r="I30" s="45">
         <f>AVERAGE(D30:H30)</f>
         <v>0.10288335015668242</v>
       </c>
+      <c r="S30" s="70"/>
+      <c r="T30" s="71"/>
+      <c r="U30" s="71"/>
+      <c r="V30" s="71"/>
+      <c r="W30" s="71"/>
+      <c r="X30" s="71"/>
+      <c r="Y30" s="72"/>
     </row>
     <row r="31" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="34" t="s">
         <v>1</v>
       </c>
       <c r="D31" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>8.0640567142450159E-2</v>
       </c>
       <c r="E31" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>8.5517645336066206E-3</v>
       </c>
       <c r="F31" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>8.6738101460638317E-2</v>
       </c>
       <c r="G31" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.13785271483539985</v>
       </c>
       <c r="H31" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.17948477091797188</v>
       </c>
       <c r="I31" s="45">
-        <f t="shared" ref="I31:I44" si="128">AVERAGE(D31:H31)</f>
+        <f t="shared" ref="I31:I44" si="46">AVERAGE(D31:H31)</f>
         <v>9.8653583778013365E-2</v>
       </c>
+      <c r="S31" s="70"/>
+      <c r="T31" s="71"/>
+      <c r="U31" s="71"/>
+      <c r="V31" s="71"/>
+      <c r="W31" s="71"/>
+      <c r="X31" s="71"/>
+      <c r="Y31" s="72"/>
     </row>
     <row r="32" spans="2:80" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="34" t="s">
         <v>2</v>
       </c>
       <c r="D32" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>5.4972856164022588E-2</v>
       </c>
       <c r="E32" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.22916666666666674</v>
       </c>
       <c r="F32" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.1198227858391252</v>
       </c>
       <c r="G32" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.23853943595513782</v>
       </c>
       <c r="H32" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>5.6179116724789813E-2</v>
       </c>
       <c r="I32" s="45">
-        <f t="shared" si="128"/>
+        <f t="shared" si="46"/>
         <v>0.13973617226994844</v>
       </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="S32" s="70"/>
+      <c r="T32" s="71"/>
+      <c r="U32" s="71"/>
+      <c r="V32" s="71"/>
+      <c r="W32" s="71"/>
+      <c r="X32" s="71"/>
+      <c r="Y32" s="72"/>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="34" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>-0.2036055143160127</v>
       </c>
       <c r="E33" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.54727030625832218</v>
       </c>
       <c r="F33" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>-0.12650602409638556</v>
       </c>
       <c r="G33" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>1.0142857142857142</v>
       </c>
       <c r="H33" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.27219369038884822</v>
       </c>
       <c r="I33" s="45">
-        <f t="shared" si="128"/>
+        <f t="shared" si="46"/>
         <v>0.30072763450409729</v>
       </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="S33" s="70"/>
+      <c r="T33" s="71"/>
+      <c r="U33" s="71"/>
+      <c r="V33" s="71"/>
+      <c r="W33" s="71"/>
+      <c r="X33" s="71"/>
+      <c r="Y33" s="72"/>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="60">
-        <f t="shared" si="127"/>
+      <c r="D34" s="54">
+        <f t="shared" si="45"/>
         <v>6.1885982118890848E-2</v>
       </c>
-      <c r="E34" s="60">
-        <f t="shared" si="127"/>
+      <c r="E34" s="54">
+        <f t="shared" si="45"/>
         <v>0.11844085540617799</v>
       </c>
-      <c r="F34" s="60">
-        <f t="shared" si="127"/>
+      <c r="F34" s="54">
+        <f t="shared" si="45"/>
         <v>0.12713971286209524</v>
       </c>
-      <c r="G34" s="60">
-        <f t="shared" si="127"/>
+      <c r="G34" s="54">
+        <f t="shared" si="45"/>
         <v>0.14640827734281014</v>
       </c>
-      <c r="H34" s="60">
-        <f t="shared" si="127"/>
+      <c r="H34" s="54">
+        <f t="shared" si="45"/>
         <v>7.7110612396467326E-2</v>
       </c>
-      <c r="I34" s="61">
-        <f t="shared" si="128"/>
+      <c r="I34" s="55">
+        <f t="shared" si="46"/>
         <v>0.10619708802528831</v>
       </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="S34" s="70"/>
+      <c r="T34" s="71"/>
+      <c r="U34" s="71"/>
+      <c r="V34" s="71"/>
+      <c r="W34" s="71"/>
+      <c r="X34" s="71"/>
+      <c r="Y34" s="72"/>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="34" t="s">
         <v>5</v>
       </c>
       <c r="D35" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>1.8895423165430802E-2</v>
       </c>
       <c r="E35" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.17262039197972356</v>
       </c>
       <c r="F35" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.12803419809428007</v>
       </c>
       <c r="G35" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.14727615939898131</v>
       </c>
       <c r="H35" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>9.215193431833768E-2</v>
       </c>
       <c r="I35" s="45">
-        <f t="shared" si="128"/>
+        <f t="shared" si="46"/>
         <v>0.11179562139135069</v>
       </c>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="O35" s="66"/>
+      <c r="P35" s="66"/>
+      <c r="Q35" s="66"/>
+      <c r="R35" s="66"/>
+      <c r="S35" s="73"/>
+      <c r="T35" s="74"/>
+      <c r="U35" s="74"/>
+      <c r="V35" s="74"/>
+      <c r="W35" s="74"/>
+      <c r="X35" s="74"/>
+      <c r="Y35" s="75"/>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="34" t="s">
         <v>6</v>
       </c>
       <c r="D36" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.18500838234876249</v>
       </c>
       <c r="E36" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>2.0981200844043757E-2</v>
       </c>
       <c r="F36" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.12219638789074416</v>
       </c>
       <c r="G36" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.14327571051860533</v>
       </c>
       <c r="H36" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>-2.956359376144102E-2</v>
       </c>
       <c r="I36" s="45">
-        <f t="shared" si="128"/>
+        <f t="shared" si="46"/>
         <v>8.8379617568142943E-2</v>
       </c>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="O36" s="66"/>
+      <c r="P36" s="66"/>
+      <c r="Q36" s="66"/>
+      <c r="R36" s="66"/>
+      <c r="S36" s="66"/>
+      <c r="T36" s="66"/>
+      <c r="U36" s="66"/>
+      <c r="V36" s="66"/>
+      <c r="W36" s="66"/>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="34" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>9.3466586051143441E-2</v>
       </c>
       <c r="E37" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>9.3999024231581352E-3</v>
       </c>
       <c r="F37" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>8.6002448926983277E-2</v>
       </c>
       <c r="G37" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.15034269946295575</v>
       </c>
       <c r="H37" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.2043848336342533</v>
       </c>
       <c r="I37" s="45">
-        <f t="shared" si="128"/>
+        <f t="shared" si="46"/>
         <v>0.10871929409969878</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>6.2867647058823639E-2</v>
       </c>
       <c r="E38" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>7.3331027326184683E-2</v>
       </c>
       <c r="F38" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>9.5713825330325575E-2</v>
       </c>
       <c r="G38" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.16823529411764704</v>
       </c>
       <c r="H38" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>3.1973816717019155E-2</v>
       </c>
       <c r="I38" s="45">
-        <f t="shared" si="128"/>
+        <f t="shared" si="46"/>
         <v>8.6424322110000021E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="D39" s="60">
-        <f t="shared" si="127"/>
+      <c r="D39" s="54">
+        <f t="shared" si="45"/>
         <v>5.5135523890861737E-2</v>
       </c>
-      <c r="E39" s="60">
-        <f t="shared" si="127"/>
+      <c r="E39" s="54">
+        <f t="shared" si="45"/>
         <v>0.12307869265898708</v>
       </c>
-      <c r="F39" s="60">
-        <f t="shared" si="127"/>
+      <c r="F39" s="54">
+        <f t="shared" si="45"/>
         <v>0.12176294537357712</v>
       </c>
-      <c r="G39" s="60">
-        <f t="shared" si="127"/>
+      <c r="G39" s="54">
+        <f t="shared" si="45"/>
         <v>0.14722024028918557</v>
       </c>
-      <c r="H39" s="60">
-        <f t="shared" si="127"/>
+      <c r="H39" s="54">
+        <f t="shared" si="45"/>
         <v>8.4674471797774098E-2</v>
       </c>
-      <c r="I39" s="61">
-        <f t="shared" si="128"/>
+      <c r="I39" s="55">
+        <f t="shared" si="46"/>
         <v>0.10637437480207712</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="60">
-        <f t="shared" si="127"/>
+      <c r="D40" s="54">
+        <f t="shared" si="45"/>
         <v>0.1381762763525527</v>
       </c>
-      <c r="E40" s="60">
-        <f t="shared" si="127"/>
+      <c r="E40" s="54">
+        <f t="shared" si="45"/>
         <v>6.9850479803615251E-2</v>
       </c>
-      <c r="F40" s="60">
-        <f t="shared" si="127"/>
+      <c r="F40" s="54">
+        <f t="shared" si="45"/>
         <v>0.18627450980392157</v>
       </c>
-      <c r="G40" s="60">
-        <f t="shared" si="127"/>
+      <c r="G40" s="54">
+        <f t="shared" si="45"/>
         <v>0.13796377703534368</v>
       </c>
-      <c r="H40" s="60">
-        <f t="shared" si="127"/>
+      <c r="H40" s="54">
+        <f t="shared" si="45"/>
         <v>-2.1942023610853623E-3</v>
       </c>
-      <c r="I40" s="61">
-        <f t="shared" si="128"/>
+      <c r="I40" s="55">
+        <f t="shared" si="46"/>
         <v>0.10601416812686956</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="34" t="s">
         <v>11</v>
       </c>
       <c r="D41" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>-2.4061032863849752E-2</v>
       </c>
       <c r="E41" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>-1.8039687312086938E-3</v>
       </c>
       <c r="F41" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.26024096385542173</v>
       </c>
       <c r="G41" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.55162523900573612</v>
       </c>
       <c r="H41" s="41">
-        <f t="shared" si="127"/>
+        <f t="shared" si="45"/>
         <v>0.20332717190388161</v>
       </c>
       <c r="I41" s="45">
-        <f t="shared" si="128"/>
+        <f t="shared" si="46"/>
         <v>0.19786567463399621</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="34" t="s">
         <v>12</v>
       </c>
@@ -4641,66 +5325,82 @@
       <c r="H42" s="41"/>
       <c r="I42" s="45"/>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="34" t="s">
         <v>13</v>
       </c>
       <c r="D43" s="41">
-        <f t="shared" ref="D43:H44" si="129">D16/C16-1</f>
+        <f t="shared" ref="D43:H44" si="47">D16/C16-1</f>
         <v>0.32896846606093</v>
       </c>
       <c r="E43" s="41">
-        <f t="shared" si="129"/>
+        <f t="shared" si="47"/>
         <v>-7.9428916147194828E-2</v>
       </c>
       <c r="F43" s="41">
-        <f t="shared" si="129"/>
+        <f t="shared" si="47"/>
         <v>0.24595893403232849</v>
       </c>
       <c r="G43" s="41">
-        <f t="shared" si="129"/>
+        <f t="shared" si="47"/>
         <v>4.628330995792429E-2</v>
       </c>
       <c r="H43" s="41">
-        <f t="shared" si="129"/>
+        <f t="shared" si="47"/>
         <v>-0.1908512064343163</v>
       </c>
       <c r="I43" s="45">
-        <f t="shared" si="128"/>
+        <f t="shared" si="46"/>
         <v>7.018611749393433E-2</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="44" spans="2:25" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B44" s="47" t="s">
         <v>14</v>
       </c>
       <c r="C44" s="48"/>
-      <c r="D44" s="62">
-        <f t="shared" si="129"/>
+      <c r="D44" s="56">
+        <f t="shared" si="47"/>
         <v>0.10745136596671112</v>
       </c>
-      <c r="E44" s="62">
-        <f t="shared" si="129"/>
+      <c r="E44" s="56">
+        <f t="shared" si="47"/>
         <v>0.12448474855729597</v>
       </c>
-      <c r="F44" s="62">
-        <f t="shared" si="129"/>
+      <c r="F44" s="56">
+        <f t="shared" si="47"/>
         <v>0.16394089781186549</v>
       </c>
-      <c r="G44" s="62">
-        <f t="shared" si="129"/>
+      <c r="G44" s="56">
+        <f t="shared" si="47"/>
         <v>0.12137215950385194</v>
       </c>
-      <c r="H44" s="62">
-        <f t="shared" si="129"/>
+      <c r="H44" s="56">
+        <f t="shared" si="47"/>
         <v>-0.34142758382302107</v>
       </c>
-      <c r="I44" s="63">
-        <f t="shared" si="128"/>
+      <c r="I44" s="57">
+        <f>AVERAGE(D44:H44)</f>
         <v>3.516431760334069E-2</v>
       </c>
+      <c r="J44" s="41"/>
+    </row>
+    <row r="49" spans="9:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="42"/>
+      <c r="L49" s="42"/>
+      <c r="M49" s="42"/>
+      <c r="N49" s="42"/>
+      <c r="O49" s="42"/>
+      <c r="P49" s="42"/>
+      <c r="Q49" s="42"/>
+      <c r="R49" s="42"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="S29:Y35"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="MAIN!A1" tooltip="click to travel to main page" display="MAIN" xr:uid="{111E8870-67FD-4E3C-8020-90F6F8E485FD}"/>
   </hyperlinks>

--- a/research/UNITEDHEALTH.xlsx
+++ b/research/UNITEDHEALTH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpilc\OneDrive - Louisiana State University\Desktop\valuation\research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145A06D0-0394-482A-A258-660E22011279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD025740-FB10-4AE0-9799-D06A557E26D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="3" xr2:uid="{4E2427E6-D2C1-49DA-B21C-AD4FF0F49230}"/>
+    <workbookView xWindow="11442" yWindow="0" windowWidth="11676" windowHeight="13758" firstSheet="2" activeTab="3" xr2:uid="{4E2427E6-D2C1-49DA-B21C-AD4FF0F49230}"/>
   </bookViews>
   <sheets>
     <sheet name="MAIN" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="152">
   <si>
     <t>PREMIUMS</t>
   </si>
@@ -194,6 +194,309 @@
   </si>
   <si>
     <t>WITH THAT EXTREMELY CONSERVATIVE GROWTH RATE, USING A ONE-TIME LOW NET INCOME AS THE BASE FOR THE GROWTH, THE COMPANY IS FAIRLY VALUED AT 325 A SHARE. THIS ISNT A DCF I MADE USING MY OWN ASSUMPTIONS, INSTEAD I START WITH THE CURRENT VALUATION THAT THE MARKET HAS GIVEN IT, THEN I BASICALLY SOLVE FOR WHAT THE MARKET'S IMPLICIT ASSUMPTIONS ARE</t>
+  </si>
+  <si>
+    <t>Cashflow Statement</t>
+  </si>
+  <si>
+    <t>Operating Activities</t>
+  </si>
+  <si>
+    <t>net income</t>
+  </si>
+  <si>
+    <t>noncash items:</t>
+  </si>
+  <si>
+    <t>deferred income taxes</t>
+  </si>
+  <si>
+    <t>share-based compensation</t>
+  </si>
+  <si>
+    <t>loss on sale of subsidiary &amp; subsidiary held for sale</t>
+  </si>
+  <si>
+    <t>gains on dispositions &amp; other strategic transactions</t>
+  </si>
+  <si>
+    <t>other, net</t>
+  </si>
+  <si>
+    <t>net change in other operating items, net of effects from acquisitions and dispositions:</t>
+  </si>
+  <si>
+    <t>accounts receivable</t>
+  </si>
+  <si>
+    <t>other assets</t>
+  </si>
+  <si>
+    <t>medical costs payable</t>
+  </si>
+  <si>
+    <t>accounts payable &amp; other liabilities</t>
+  </si>
+  <si>
+    <t>unearned revenues</t>
+  </si>
+  <si>
+    <t>cash flows from operating activities</t>
+  </si>
+  <si>
+    <t>investing activities</t>
+  </si>
+  <si>
+    <t>purchases of investments</t>
+  </si>
+  <si>
+    <t>sales of investments</t>
+  </si>
+  <si>
+    <t>maturities of investments</t>
+  </si>
+  <si>
+    <t>cash paid for acquisitions and other transactions, net of cash assumed</t>
+  </si>
+  <si>
+    <t>purchases of property, equipment, and capitalized software</t>
+  </si>
+  <si>
+    <t>loans to care providers - cyberattack</t>
+  </si>
+  <si>
+    <t>repayments of care provider loans - cyberattack</t>
+  </si>
+  <si>
+    <t>cash received from dispositions &amp; other strategic transactions, net</t>
+  </si>
+  <si>
+    <t>cash flows used for investing activities</t>
+  </si>
+  <si>
+    <t>financing activities</t>
+  </si>
+  <si>
+    <t>common share repurchases</t>
+  </si>
+  <si>
+    <t>cash dividends paid</t>
+  </si>
+  <si>
+    <t>proceeds from common stock issuances</t>
+  </si>
+  <si>
+    <t>repayments of long-term debt</t>
+  </si>
+  <si>
+    <t>(repayments of) proceeds from short-term borrowings, net</t>
+  </si>
+  <si>
+    <t>proceeder from issuance of long-term debt</t>
+  </si>
+  <si>
+    <t>customer funds administered</t>
+  </si>
+  <si>
+    <t>purchases of redeemable noncontrolling interests</t>
+  </si>
+  <si>
+    <t>cash flows (used for) from financing activities</t>
+  </si>
+  <si>
+    <t>effect of exchange rate changes on cash &amp; cash equivalents</t>
+  </si>
+  <si>
+    <t>increase in cash &amp; cash equivalents, including cash within businesses held for sale</t>
+  </si>
+  <si>
+    <t>less: cash within businesses held for sale</t>
+  </si>
+  <si>
+    <t>net (decrease) increase in cash &amp; cash equivalents</t>
+  </si>
+  <si>
+    <t>cash &amp; cash equivalents, beginning of period</t>
+  </si>
+  <si>
+    <t>cash &amp; cash equivalents, end of period</t>
+  </si>
+  <si>
+    <t>supplemental cash flow disclosures</t>
+  </si>
+  <si>
+    <t>cash paid for interest</t>
+  </si>
+  <si>
+    <t>cash paid for income taxes</t>
+  </si>
+  <si>
+    <t>Balance Sheet</t>
+  </si>
+  <si>
+    <t>Assets</t>
+  </si>
+  <si>
+    <t>current assets</t>
+  </si>
+  <si>
+    <t>short-term investments</t>
+  </si>
+  <si>
+    <t>cash &amp; cash equivalents</t>
+  </si>
+  <si>
+    <t>accounts receivable, net</t>
+  </si>
+  <si>
+    <t>assets under management</t>
+  </si>
+  <si>
+    <t>prepaid expenses &amp; other current assets</t>
+  </si>
+  <si>
+    <t>total current assets</t>
+  </si>
+  <si>
+    <t>long-term investments</t>
+  </si>
+  <si>
+    <t>property, equipment, &amp; capitalized software, gross</t>
+  </si>
+  <si>
+    <t>accumulated depreciation &amp; amortization</t>
+  </si>
+  <si>
+    <t>property, equipment, &amp; capitalized software, net</t>
+  </si>
+  <si>
+    <t>goodwill</t>
+  </si>
+  <si>
+    <t>other intangible assets, gross</t>
+  </si>
+  <si>
+    <t>accumulated amortization</t>
+  </si>
+  <si>
+    <t>other intangible assets, net</t>
+  </si>
+  <si>
+    <t>total assets</t>
+  </si>
+  <si>
+    <t>liabilities, redeemable noncontrolling interests and equity</t>
+  </si>
+  <si>
+    <t>current liabilities</t>
+  </si>
+  <si>
+    <t>accounts payable &amp; accrued liabilities</t>
+  </si>
+  <si>
+    <t>short-term borrowings &amp; current maturities of long-term debt</t>
+  </si>
+  <si>
+    <t>other current liabilities</t>
+  </si>
+  <si>
+    <t>total current liabilities</t>
+  </si>
+  <si>
+    <t>long-term debt, less current maturities</t>
+  </si>
+  <si>
+    <t>other liabilities</t>
+  </si>
+  <si>
+    <t>total liabilities</t>
+  </si>
+  <si>
+    <t>commitments &amp; contingencies</t>
+  </si>
+  <si>
+    <t>redeemable noncontrolling interests</t>
+  </si>
+  <si>
+    <t>equity:</t>
+  </si>
+  <si>
+    <t>preferred stock</t>
+  </si>
+  <si>
+    <t>common stock</t>
+  </si>
+  <si>
+    <t>retained earnings</t>
+  </si>
+  <si>
+    <t>accumulated other comprehensive loss</t>
+  </si>
+  <si>
+    <t>nonredeemable noncontrolling interests</t>
+  </si>
+  <si>
+    <t>total equity</t>
+  </si>
+  <si>
+    <t>total liabilities, redeemable noncontrolling interests, &amp; equity</t>
+  </si>
+  <si>
+    <t>other current receivables, net</t>
+  </si>
+  <si>
+    <t>PP&amp;E schedule</t>
+  </si>
+  <si>
+    <t>land &amp; improvements</t>
+  </si>
+  <si>
+    <t>buildings &amp; improvements</t>
+  </si>
+  <si>
+    <t>computer equipment</t>
+  </si>
+  <si>
+    <t>furniture &amp; fixtures</t>
+  </si>
+  <si>
+    <t>less accumulated depreciation</t>
+  </si>
+  <si>
+    <t>property and equipment, net</t>
+  </si>
+  <si>
+    <t>capitalized software</t>
+  </si>
+  <si>
+    <t>capitalized software, net</t>
+  </si>
+  <si>
+    <t>total property, equipment, &amp; capitalized software, net</t>
+  </si>
+  <si>
+    <t>Goodwill &amp; Other intangible assets schedule</t>
+  </si>
+  <si>
+    <t>beginning balance</t>
+  </si>
+  <si>
+    <t>acquisitions</t>
+  </si>
+  <si>
+    <t>dispositions, foreign currency effects &amp; other adjustements, net</t>
+  </si>
+  <si>
+    <t>ending balance</t>
+  </si>
+  <si>
+    <t>Double check</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>depreciation &amp; amortization</t>
   </si>
 </sst>
 </file>
@@ -672,6 +975,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -680,9 +986,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -696,7 +999,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
@@ -796,7 +1099,7 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>223</xdr:row>
       <xdr:rowOff>125406</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -846,7 +1149,7 @@
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>223</xdr:row>
       <xdr:rowOff>125406</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1361,7 +1664,7 @@
       <c r="C6" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="64" t="s">
         <v>39</v>
       </c>
       <c r="E6" s="36">
@@ -1375,7 +1678,7 @@
       <c r="C7" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="64"/>
+      <c r="D7" s="65"/>
       <c r="E7" s="36">
         <f>E5*E6</f>
         <v>280641.05519175</v>
@@ -1386,7 +1689,7 @@
       <c r="C8" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="64"/>
+      <c r="D8" s="65"/>
       <c r="E8" s="36">
         <f>28596+3424</f>
         <v>32020</v>
@@ -1399,7 +1702,7 @@
       <c r="C9" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="64"/>
+      <c r="D9" s="65"/>
       <c r="E9" s="36">
         <f>73495+5698</f>
         <v>79193</v>
@@ -1412,7 +1715,7 @@
       <c r="C10" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="65"/>
+      <c r="D10" s="66"/>
       <c r="E10" s="37">
         <f>E7-E8+E9</f>
         <v>327814.05519175</v>
@@ -3017,13 +3320,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0888499-3247-4B46-B85D-44CAD6C9F224}">
-  <dimension ref="A1:CB49"/>
+  <dimension ref="A1:CB180"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="5.3125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.3671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="69.9453125" bestFit="1" customWidth="1"/>
     <col min="3" max="18" width="7.83984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.47265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.83984375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="7.734375" bestFit="1" customWidth="1"/>
     <col min="21" max="79" width="6.83984375" bestFit="1" customWidth="1"/>
     <col min="80" max="80" width="7.83984375" bestFit="1" customWidth="1"/>
@@ -3506,6 +3809,9 @@
       </c>
     </row>
     <row r="3" spans="1:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>150</v>
+      </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -4374,7 +4680,7 @@
       <c r="Z16" s="62"/>
       <c r="AA16" s="62"/>
     </row>
-    <row r="17" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B17" s="9" t="s">
         <v>14</v>
       </c>
@@ -4443,963 +4749,2793 @@
         <v>54417.690522991179</v>
       </c>
       <c r="S17" s="53">
-        <f>R17*(1+$T$21)</f>
+        <f>R17*(1+$T$152)</f>
         <v>54961.867428221092</v>
       </c>
       <c r="T17" s="53">
-        <f>S17*(1+$T$21)</f>
+        <f>S17*(1+$T$152)</f>
         <v>55511.486102503302</v>
       </c>
       <c r="U17" s="53">
-        <f>T17*(1+$T$21)</f>
+        <f>T17*(1+$T$152)</f>
         <v>56066.600963528334</v>
       </c>
       <c r="V17" s="53">
-        <f>U17*(1+$T$21)</f>
+        <f>U17*(1+$T$152)</f>
         <v>56627.26697316362</v>
       </c>
       <c r="W17" s="53">
-        <f>V17*(1+$T$21)</f>
+        <f>V17*(1+$T$152)</f>
         <v>57193.539642895259</v>
       </c>
       <c r="X17" s="53">
-        <f>W17*(1+$T$21)</f>
+        <f>W17*(1+$T$152)</f>
         <v>57765.475039324214</v>
       </c>
       <c r="Y17" s="53">
-        <f>X17*(1+$T$21)</f>
+        <f>X17*(1+$T$152)</f>
         <v>58343.129789717459</v>
       </c>
       <c r="Z17" s="53">
-        <f>Y17*(1+$T$21)</f>
+        <f>Y17*(1+$T$152)</f>
         <v>58926.561087614631</v>
       </c>
       <c r="AA17" s="53">
-        <f>Z17*(1+$T$21)</f>
+        <f>Z17*(1+$T$152)</f>
         <v>59515.826698490775</v>
       </c>
       <c r="AB17" s="53">
-        <f>AA17*(1+$T$21)</f>
+        <f>AA17*(1+$T$152)</f>
         <v>60110.984965475684</v>
       </c>
       <c r="AC17" s="53">
-        <f>AB17*(1+$T$21)</f>
+        <f>AB17*(1+$T$152)</f>
         <v>60712.09481513044</v>
       </c>
       <c r="AD17" s="53">
-        <f>AC17*(1+$T$21)</f>
+        <f>AC17*(1+$T$152)</f>
         <v>61319.215763281747</v>
       </c>
       <c r="AE17" s="53">
-        <f>AD17*(1+$T$21)</f>
+        <f>AD17*(1+$T$152)</f>
         <v>61932.407920914564</v>
       </c>
       <c r="AF17" s="53">
-        <f>AE17*(1+$T$21)</f>
+        <f>AE17*(1+$T$152)</f>
         <v>62551.732000123709</v>
       </c>
       <c r="AG17" s="53">
-        <f>AF17*(1+$T$21)</f>
+        <f>AF17*(1+$T$152)</f>
         <v>63177.249320124945</v>
       </c>
       <c r="AH17" s="53">
-        <f>AG17*(1+$T$21)</f>
+        <f>AG17*(1+$T$152)</f>
         <v>63809.021813326195</v>
       </c>
       <c r="AI17" s="53">
-        <f>AH17*(1+$T$21)</f>
+        <f>AH17*(1+$T$152)</f>
         <v>64447.112031459459</v>
       </c>
       <c r="AJ17" s="53">
-        <f>AI17*(1+$T$21)</f>
+        <f>AI17*(1+$T$152)</f>
         <v>65091.583151774052</v>
       </c>
       <c r="AK17" s="53">
-        <f>AJ17*(1+$T$21)</f>
+        <f>AJ17*(1+$T$152)</f>
         <v>65742.498983291793</v>
       </c>
       <c r="AL17" s="53">
-        <f>AK17*(1+$T$21)</f>
+        <f>AK17*(1+$T$152)</f>
         <v>66399.923973124707</v>
       </c>
       <c r="AM17" s="53">
-        <f>AL17*(1+$T$21)</f>
+        <f>AL17*(1+$T$152)</f>
         <v>67063.923212855952</v>
       </c>
       <c r="AN17" s="53">
-        <f>AM17*(1+$T$21)</f>
+        <f>AM17*(1+$T$152)</f>
         <v>67734.562444984505</v>
       </c>
       <c r="AO17" s="53">
-        <f>AN17*(1+$T$21)</f>
+        <f>AN17*(1+$T$152)</f>
         <v>68411.908069434357</v>
       </c>
       <c r="AP17" s="53">
-        <f>AO17*(1+$T$21)</f>
+        <f>AO17*(1+$T$152)</f>
         <v>69096.027150128706</v>
       </c>
       <c r="AQ17" s="53">
-        <f>AP17*(1+$T$21)</f>
+        <f>AP17*(1+$T$152)</f>
         <v>69786.987421629994</v>
       </c>
       <c r="AR17" s="53">
-        <f>AQ17*(1+$T$21)</f>
+        <f>AQ17*(1+$T$152)</f>
         <v>70484.85729584629</v>
       </c>
       <c r="AS17" s="53">
-        <f>AR17*(1+$T$21)</f>
+        <f>AR17*(1+$T$152)</f>
         <v>71189.705868804755</v>
       </c>
       <c r="AT17" s="53">
-        <f>AS17*(1+$T$21)</f>
+        <f>AS17*(1+$T$152)</f>
         <v>71901.602927492801</v>
       </c>
       <c r="AU17" s="53">
-        <f>AT17*(1+$T$21)</f>
+        <f>AT17*(1+$T$152)</f>
         <v>72620.618956767736</v>
       </c>
       <c r="AV17" s="53">
-        <f>AU17*(1+$T$21)</f>
+        <f>AU17*(1+$T$152)</f>
         <v>73346.82514633541</v>
       </c>
       <c r="AW17" s="53">
-        <f>AV17*(1+$T$21)</f>
+        <f>AV17*(1+$T$152)</f>
         <v>74080.29339779877</v>
       </c>
       <c r="AX17" s="53">
-        <f>AW17*(1+$T$21)</f>
+        <f>AW17*(1+$T$152)</f>
         <v>74821.09633177676</v>
       </c>
       <c r="AY17" s="53">
-        <f>AX17*(1+$T$21)</f>
+        <f>AX17*(1+$T$152)</f>
         <v>75569.307295094535</v>
       </c>
       <c r="AZ17" s="53">
-        <f>AY17*(1+$T$21)</f>
+        <f>AY17*(1+$T$152)</f>
         <v>76325.000368045483</v>
       </c>
       <c r="BA17" s="53">
-        <f>AZ17*(1+$T$21)</f>
+        <f>AZ17*(1+$T$152)</f>
         <v>77088.250371725939</v>
       </c>
       <c r="BB17" s="53">
-        <f>BA17*(1+$T$21)</f>
+        <f>BA17*(1+$T$152)</f>
         <v>77859.132875443203</v>
       </c>
       <c r="BC17" s="53">
-        <f>BB17*(1+$T$21)</f>
+        <f>BB17*(1+$T$152)</f>
         <v>78637.724204197642</v>
       </c>
       <c r="BD17" s="53">
-        <f>BC17*(1+$T$21)</f>
+        <f>BC17*(1+$T$152)</f>
         <v>79424.101446239612</v>
       </c>
       <c r="BE17" s="53">
-        <f>BD17*(1+$T$21)</f>
+        <f>BD17*(1+$T$152)</f>
         <v>80218.342460702013</v>
       </c>
       <c r="BF17" s="53">
-        <f>BE17*(1+$T$21)</f>
+        <f>BE17*(1+$T$152)</f>
         <v>81020.525885309034</v>
       </c>
       <c r="BG17" s="53">
-        <f>BF17*(1+$T$21)</f>
+        <f>BF17*(1+$T$152)</f>
         <v>81830.731144162128</v>
       </c>
       <c r="BH17" s="53">
-        <f>BG17*(1+$T$21)</f>
+        <f>BG17*(1+$T$152)</f>
         <v>82649.038455603746</v>
       </c>
       <c r="BI17" s="53">
-        <f>BH17*(1+$T$21)</f>
+        <f>BH17*(1+$T$152)</f>
         <v>83475.528840159779</v>
       </c>
       <c r="BJ17" s="53">
-        <f>BI17*(1+$T$21)</f>
+        <f>BI17*(1+$T$152)</f>
         <v>84310.284128561383</v>
       </c>
       <c r="BK17" s="53">
-        <f>BJ17*(1+$T$21)</f>
+        <f>BJ17*(1+$T$152)</f>
         <v>85153.386969846993</v>
       </c>
       <c r="BL17" s="53">
-        <f>BK17*(1+$T$21)</f>
+        <f>BK17*(1+$T$152)</f>
         <v>86004.920839545463</v>
       </c>
       <c r="BM17" s="53">
-        <f>BL17*(1+$T$21)</f>
+        <f>BL17*(1+$T$152)</f>
         <v>86864.970047940922</v>
       </c>
       <c r="BN17" s="53">
-        <f>BM17*(1+$T$21)</f>
+        <f>BM17*(1+$T$152)</f>
         <v>87733.619748420329</v>
       </c>
       <c r="BO17" s="53">
-        <f>BN17*(1+$T$21)</f>
+        <f>BN17*(1+$T$152)</f>
         <v>88610.955945904527</v>
       </c>
       <c r="BP17" s="53">
-        <f>BO17*(1+$T$21)</f>
+        <f>BO17*(1+$T$152)</f>
         <v>89497.065505363571</v>
       </c>
       <c r="BQ17" s="53">
-        <f>BP17*(1+$T$21)</f>
+        <f>BP17*(1+$T$152)</f>
         <v>90392.036160417207</v>
       </c>
       <c r="BR17" s="53">
-        <f>BQ17*(1+$T$21)</f>
+        <f>BQ17*(1+$T$152)</f>
         <v>91295.956522021384</v>
       </c>
       <c r="BS17" s="53">
-        <f>BR17*(1+$T$21)</f>
+        <f>BR17*(1+$T$152)</f>
         <v>92208.916087241596</v>
       </c>
       <c r="BT17" s="53">
-        <f>BS17*(1+$T$21)</f>
+        <f>BS17*(1+$T$152)</f>
         <v>93131.005248114016</v>
       </c>
       <c r="BU17" s="53">
-        <f>BT17*(1+$T$21)</f>
+        <f>BT17*(1+$T$152)</f>
         <v>94062.315300595161</v>
       </c>
       <c r="BV17" s="53">
-        <f>BU17*(1+$T$21)</f>
+        <f>BU17*(1+$T$152)</f>
         <v>95002.93845360112</v>
       </c>
       <c r="BW17" s="53">
-        <f>BV17*(1+$T$21)</f>
+        <f>BV17*(1+$T$152)</f>
         <v>95952.967838137134</v>
       </c>
       <c r="BX17" s="53">
-        <f>BW17*(1+$T$21)</f>
+        <f>BW17*(1+$T$152)</f>
         <v>96912.497516518502</v>
       </c>
       <c r="BY17" s="53">
-        <f>BX17*(1+$T$21)</f>
+        <f>BX17*(1+$T$152)</f>
         <v>97881.622491683695</v>
       </c>
       <c r="BZ17" s="53">
-        <f>BY17*(1+$T$21)</f>
+        <f>BY17*(1+$T$152)</f>
         <v>98860.438716600533</v>
       </c>
       <c r="CA17" s="53">
-        <f>BZ17*(1+$T$21)</f>
+        <f>BZ17*(1+$T$152)</f>
         <v>99849.04310376654</v>
       </c>
       <c r="CB17" s="53">
-        <f>CA17*(1+$T$21)</f>
+        <f>CA17*(1+$T$152)</f>
         <v>100847.53353480421</v>
       </c>
     </row>
-    <row r="18" spans="2:80" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="19" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="J20" s="41"/>
-      <c r="K20" s="41"/>
-      <c r="L20" s="41"/>
-      <c r="M20" s="41"/>
-      <c r="S20" s="58" t="s">
+    <row r="18" spans="1:80" ht="14.7" thickTop="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="19" spans="1:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23">
+        <v>16921</v>
+      </c>
+      <c r="E23">
+        <v>21375</v>
+      </c>
+      <c r="F23">
+        <v>23365</v>
+      </c>
+      <c r="G23">
+        <v>25427</v>
+      </c>
+      <c r="H23">
+        <v>25312</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24">
+        <v>2860</v>
+      </c>
+      <c r="E24">
+        <v>2532</v>
+      </c>
+      <c r="G24">
+        <v>4201</v>
+      </c>
+      <c r="H24">
+        <v>3801</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25">
+        <v>12870</v>
+      </c>
+      <c r="E25">
+        <v>14216</v>
+      </c>
+      <c r="G25">
+        <v>21276</v>
+      </c>
+      <c r="H25">
+        <v>22365</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" t="s">
+        <v>133</v>
+      </c>
+      <c r="D26">
+        <v>12534</v>
+      </c>
+      <c r="E26">
+        <v>13866</v>
+      </c>
+      <c r="G26">
+        <v>17694</v>
+      </c>
+      <c r="H26">
+        <v>26089</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27">
+        <v>4076</v>
+      </c>
+      <c r="E27">
+        <v>4449</v>
+      </c>
+      <c r="G27">
+        <v>3755</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28">
+        <v>4457</v>
+      </c>
+      <c r="E28">
+        <v>5320</v>
+      </c>
+      <c r="G28">
+        <v>6084</v>
+      </c>
+      <c r="H28">
+        <v>8212</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29">
+        <f>SUM(D23:D28)</f>
+        <v>53718</v>
+      </c>
+      <c r="E29">
+        <f>SUM(E23:E28)</f>
+        <v>61758</v>
+      </c>
+      <c r="F29">
+        <f>SUM(F23:F28)</f>
+        <v>23365</v>
+      </c>
+      <c r="G29">
+        <f>SUM(G23:G28)</f>
+        <v>78437</v>
+      </c>
+      <c r="H29">
+        <f>SUM(H23:H28)</f>
+        <v>85779</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="D30">
+        <v>41242</v>
+      </c>
+      <c r="E30">
+        <v>43114</v>
+      </c>
+      <c r="G30">
+        <v>47609</v>
+      </c>
+      <c r="H30">
+        <v>52354</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33">
+        <v>8626</v>
+      </c>
+      <c r="E33">
+        <v>8969</v>
+      </c>
+      <c r="G33">
+        <v>11450</v>
+      </c>
+      <c r="H33">
+        <v>10553</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34">
+        <v>71337</v>
+      </c>
+      <c r="E34">
+        <v>75795</v>
+      </c>
+      <c r="G34">
+        <v>103732</v>
+      </c>
+      <c r="H34">
+        <v>106734</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37">
+        <v>10856</v>
+      </c>
+      <c r="E37">
+        <v>10044</v>
+      </c>
+      <c r="G37">
+        <v>15194</v>
+      </c>
+      <c r="H37">
+        <v>23268</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38">
+        <v>11510</v>
+      </c>
+      <c r="E38">
+        <v>12526</v>
+      </c>
+      <c r="G38">
+        <v>17298</v>
+      </c>
+      <c r="H38">
+        <v>19590</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39">
+        <f>D29+D30+D33+D34+D37+D38</f>
+        <v>197289</v>
+      </c>
+      <c r="E39">
+        <f>E29+E30+E33+E34+E37+E38</f>
+        <v>212206</v>
+      </c>
+      <c r="F39">
+        <f>F29+F30+F33+F34+F37+F38</f>
+        <v>23365</v>
+      </c>
+      <c r="G39">
+        <f>G29+G30+G33+G34+G37+G38</f>
+        <v>273720</v>
+      </c>
+      <c r="H39">
+        <f>H29+H30+H33+H34+H37+H38</f>
+        <v>298278</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42">
+        <v>21872</v>
+      </c>
+      <c r="E42">
+        <v>24483</v>
+      </c>
+      <c r="G42">
+        <v>32395</v>
+      </c>
+      <c r="H42">
+        <v>34224</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43">
+        <v>22495</v>
+      </c>
+      <c r="E43">
+        <v>24643</v>
+      </c>
+      <c r="G43">
+        <v>31958</v>
+      </c>
+      <c r="H43">
+        <v>34337</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" t="s">
+        <v>117</v>
+      </c>
+      <c r="D44">
+        <v>4819</v>
+      </c>
+      <c r="E44">
+        <v>3620</v>
+      </c>
+      <c r="G44">
+        <v>4274</v>
+      </c>
+      <c r="H44">
+        <v>4545</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45">
+        <v>2842</v>
+      </c>
+      <c r="E45">
+        <v>2571</v>
+      </c>
+      <c r="G45">
+        <v>3355</v>
+      </c>
+      <c r="H45">
+        <v>3317</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" t="s">
+        <v>118</v>
+      </c>
+      <c r="D46">
+        <v>20392</v>
+      </c>
+      <c r="E46">
+        <v>22975</v>
+      </c>
+      <c r="G46">
+        <v>27072</v>
+      </c>
+      <c r="H46">
+        <v>27346</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" t="s">
+        <v>119</v>
+      </c>
+      <c r="D47">
+        <f>SUM(D42:D46)</f>
+        <v>72420</v>
+      </c>
+      <c r="E47">
+        <f>SUM(E42:E46)</f>
+        <v>78292</v>
+      </c>
+      <c r="F47">
+        <f>SUM(F42:F46)</f>
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <f>SUM(G42:G46)</f>
+        <v>99054</v>
+      </c>
+      <c r="H47">
+        <f>SUM(H42:H46)</f>
+        <v>103769</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" t="s">
+        <v>120</v>
+      </c>
+      <c r="D48">
+        <v>38648</v>
+      </c>
+      <c r="E48">
+        <v>42383</v>
+      </c>
+      <c r="G48">
+        <v>58263</v>
+      </c>
+      <c r="H48">
+        <v>72359</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49">
+        <v>3367</v>
+      </c>
+      <c r="E49">
+        <v>3265</v>
+      </c>
+      <c r="G49">
+        <v>3021</v>
+      </c>
+      <c r="H49">
+        <v>3620</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50">
+        <v>12315</v>
+      </c>
+      <c r="E50">
+        <v>11787</v>
+      </c>
+      <c r="G50">
+        <v>14463</v>
+      </c>
+      <c r="H50">
+        <v>15939</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" t="s">
+        <v>122</v>
+      </c>
+      <c r="D51">
+        <f>SUM(D47:D50)</f>
+        <v>126750</v>
+      </c>
+      <c r="E51">
+        <f>SUM(E47:E50)</f>
+        <v>135727</v>
+      </c>
+      <c r="F51">
+        <f>SUM(F47:F50)</f>
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <f>SUM(G47:G50)</f>
+        <v>174801</v>
+      </c>
+      <c r="H51">
+        <f>SUM(H47:H50)</f>
+        <v>195687</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" t="s">
+        <v>124</v>
+      </c>
+      <c r="D53">
+        <v>2211</v>
+      </c>
+      <c r="E53">
+        <v>1434</v>
+      </c>
+      <c r="G53">
+        <v>4498</v>
+      </c>
+      <c r="H53">
+        <v>4323</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" t="s">
+        <v>126</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" t="s">
+        <v>127</v>
+      </c>
+      <c r="D56">
+        <v>10</v>
+      </c>
+      <c r="E56">
+        <v>10</v>
+      </c>
+      <c r="G56">
+        <v>9</v>
+      </c>
+      <c r="H56">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" t="s">
+        <v>128</v>
+      </c>
+      <c r="D57">
+        <v>69295</v>
+      </c>
+      <c r="E57">
+        <v>77134</v>
+      </c>
+      <c r="G57">
+        <v>95774</v>
+      </c>
+      <c r="H57">
+        <v>96036</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" t="s">
+        <v>129</v>
+      </c>
+      <c r="D58">
+        <v>-3814</v>
+      </c>
+      <c r="E58">
+        <v>-5384</v>
+      </c>
+      <c r="G58">
+        <v>-7027</v>
+      </c>
+      <c r="H58">
+        <v>-3387</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" t="s">
+        <v>130</v>
+      </c>
+      <c r="D59">
+        <v>2837</v>
+      </c>
+      <c r="E59">
+        <v>3285</v>
+      </c>
+      <c r="G59">
+        <v>5665</v>
+      </c>
+      <c r="H59">
+        <v>5610</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" t="s">
+        <v>131</v>
+      </c>
+      <c r="D60">
+        <f>SUM(D55:D59)</f>
+        <v>68328</v>
+      </c>
+      <c r="E60">
+        <f>SUM(E55:E59)</f>
+        <v>75045</v>
+      </c>
+      <c r="F60">
+        <f>SUM(F55:F59)</f>
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <f>SUM(G55:G59)</f>
+        <v>94421</v>
+      </c>
+      <c r="H60">
+        <f>SUM(H55:H59)</f>
+        <v>98268</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" t="s">
+        <v>132</v>
+      </c>
+      <c r="D61">
+        <f>D60+D53+D51</f>
+        <v>197289</v>
+      </c>
+      <c r="E61">
+        <f>E60+E53+E51</f>
+        <v>212206</v>
+      </c>
+      <c r="F61">
+        <f>F60+F53+F51</f>
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <f>G60+G53+G51</f>
+        <v>273720</v>
+      </c>
+      <c r="H61">
+        <f>H60+H53+H51</f>
+        <v>298278</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>150</v>
+      </c>
+      <c r="B63" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" t="s">
+        <v>135</v>
+      </c>
+      <c r="D64">
+        <v>533</v>
+      </c>
+      <c r="E64">
+        <v>502</v>
+      </c>
+      <c r="G64">
+        <v>712</v>
+      </c>
+      <c r="H64">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" t="s">
+        <v>136</v>
+      </c>
+      <c r="D65">
+        <v>4759</v>
+      </c>
+      <c r="E65">
+        <v>4882</v>
+      </c>
+      <c r="G65">
+        <v>5573</v>
+      </c>
+      <c r="H65">
+        <v>4215</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" t="s">
+        <v>137</v>
+      </c>
+      <c r="D66">
+        <v>1767</v>
+      </c>
+      <c r="E66">
+        <v>1851</v>
+      </c>
+      <c r="G66">
+        <v>2007</v>
+      </c>
+      <c r="H66">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" t="s">
+        <v>138</v>
+      </c>
+      <c r="D67">
+        <v>1787</v>
+      </c>
+      <c r="E67">
+        <v>2014</v>
+      </c>
+      <c r="G67">
+        <v>2375</v>
+      </c>
+      <c r="H67">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" t="s">
+        <v>139</v>
+      </c>
+      <c r="D68">
+        <v>-3364</v>
+      </c>
+      <c r="E68">
+        <v>-3857</v>
+      </c>
+      <c r="G68">
+        <v>-4210</v>
+      </c>
+      <c r="H68">
+        <v>-3645</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" t="s">
+        <v>140</v>
+      </c>
+      <c r="D69">
+        <f>SUM(D64:D68)</f>
+        <v>5482</v>
+      </c>
+      <c r="E69">
+        <f>SUM(E64:E68)</f>
+        <v>5392</v>
+      </c>
+      <c r="G69">
+        <f>SUM(G64:G68)</f>
+        <v>6457</v>
+      </c>
+      <c r="H69">
+        <f>SUM(H64:H68)</f>
+        <v>4895</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" t="s">
+        <v>141</v>
+      </c>
+      <c r="D70">
+        <v>5010</v>
+      </c>
+      <c r="E70">
+        <v>5712</v>
+      </c>
+      <c r="G70">
+        <v>7822</v>
+      </c>
+      <c r="H70">
+        <v>8984</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" t="s">
+        <v>139</v>
+      </c>
+      <c r="D71">
+        <v>-1866</v>
+      </c>
+      <c r="E71">
+        <v>-2135</v>
+      </c>
+      <c r="G71">
+        <v>-2829</v>
+      </c>
+      <c r="H71">
+        <v>-3326</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" t="s">
+        <v>142</v>
+      </c>
+      <c r="D72">
+        <f>SUM(D70:D71)</f>
+        <v>3144</v>
+      </c>
+      <c r="E72">
+        <f>SUM(E70:E71)</f>
+        <v>3577</v>
+      </c>
+      <c r="G72">
+        <f>SUM(G70:G71)</f>
+        <v>4993</v>
+      </c>
+      <c r="H72">
+        <f>SUM(H70:H71)</f>
+        <v>5658</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" t="s">
+        <v>143</v>
+      </c>
+      <c r="D73">
+        <f>D72+D69</f>
+        <v>8626</v>
+      </c>
+      <c r="E73">
+        <f>E72+E69</f>
+        <v>8969</v>
+      </c>
+      <c r="F73">
+        <f>F72+F69</f>
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <f>G72+G69</f>
+        <v>11450</v>
+      </c>
+      <c r="H73">
+        <f>H72+H69</f>
+        <v>10553</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" t="s">
+        <v>145</v>
+      </c>
+      <c r="D76">
+        <v>65659</v>
+      </c>
+      <c r="E76">
+        <f>D79</f>
+        <v>71337</v>
+      </c>
+      <c r="F76">
+        <f>E79</f>
+        <v>75795</v>
+      </c>
+      <c r="G76">
+        <v>93352</v>
+      </c>
+      <c r="H76">
+        <v>103732</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" t="s">
+        <v>146</v>
+      </c>
+      <c r="D77">
+        <v>6379</v>
+      </c>
+      <c r="E77">
+        <v>4804</v>
+      </c>
+      <c r="G77">
+        <v>10121</v>
+      </c>
+      <c r="H77">
+        <v>4376</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" t="s">
+        <v>147</v>
+      </c>
+      <c r="D78">
+        <v>-701</v>
+      </c>
+      <c r="E78">
+        <v>-346</v>
+      </c>
+      <c r="G78">
+        <v>259</v>
+      </c>
+      <c r="H78">
+        <v>-1374</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" t="s">
+        <v>148</v>
+      </c>
+      <c r="D79">
+        <f>SUM(D76:D78)</f>
+        <v>71337</v>
+      </c>
+      <c r="E79">
+        <f>SUM(E76:E78)</f>
+        <v>75795</v>
+      </c>
+      <c r="F79">
+        <f>SUM(F76:F78)</f>
+        <v>75795</v>
+      </c>
+      <c r="G79">
+        <f>SUM(G76:G78)</f>
+        <v>103732</v>
+      </c>
+      <c r="H79">
+        <f>SUM(H76:H78)</f>
+        <v>106734</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" t="s">
+        <v>150</v>
+      </c>
+      <c r="B82" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" t="s">
+        <v>53</v>
+      </c>
+      <c r="D84">
+        <v>15769</v>
+      </c>
+      <c r="E84" s="1">
+        <f>E17</f>
+        <v>17732</v>
+      </c>
+      <c r="F84" s="1">
+        <f>F17</f>
+        <v>20639</v>
+      </c>
+      <c r="G84" s="1">
+        <f>G17</f>
+        <v>23144</v>
+      </c>
+      <c r="H84" s="1">
+        <f>H17</f>
+        <v>15242</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" t="s">
+        <v>151</v>
+      </c>
+      <c r="D86">
+        <v>2891</v>
+      </c>
+      <c r="E86" s="1">
+        <f>E11</f>
+        <v>3103</v>
+      </c>
+      <c r="F86">
+        <v>3400</v>
+      </c>
+      <c r="G86">
+        <v>3972</v>
+      </c>
+      <c r="H86">
+        <v>4099</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" t="s">
+        <v>55</v>
+      </c>
+      <c r="D87">
+        <v>-8</v>
+      </c>
+      <c r="E87">
+        <f>D49-E49</f>
+        <v>102</v>
+      </c>
+      <c r="F87">
+        <v>-673</v>
+      </c>
+      <c r="G87">
+        <v>-245</v>
+      </c>
+      <c r="H87">
+        <v>-296</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" t="s">
+        <v>56</v>
+      </c>
+      <c r="D88">
+        <v>679</v>
+      </c>
+      <c r="E88">
+        <v>800</v>
+      </c>
+      <c r="F88">
+        <v>925</v>
+      </c>
+      <c r="G88">
+        <v>1059</v>
+      </c>
+      <c r="H88">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" t="s">
+        <v>57</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>8310</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" t="s">
+        <v>58</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>-588</v>
+      </c>
+      <c r="G90">
+        <v>-489</v>
+      </c>
+      <c r="H90">
+        <v>-3333</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" t="s">
+        <v>59</v>
+      </c>
+      <c r="D91">
+        <v>-52</v>
+      </c>
+      <c r="E91">
+        <v>-944</v>
+      </c>
+      <c r="F91">
+        <v>257</v>
+      </c>
+      <c r="G91">
+        <v>-16</v>
+      </c>
+      <c r="H91">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" t="s">
+        <v>61</v>
+      </c>
+      <c r="D93">
+        <v>-688</v>
+      </c>
+      <c r="E93">
+        <v>-1000</v>
+      </c>
+      <c r="F93">
+        <v>-2523</v>
+      </c>
+      <c r="G93">
+        <v>-3114</v>
+      </c>
+      <c r="H93">
+        <v>-1437</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" t="s">
+        <v>62</v>
+      </c>
+      <c r="D94">
+        <v>-2195</v>
+      </c>
+      <c r="E94">
+        <v>-1031</v>
+      </c>
+      <c r="F94">
+        <v>-1374</v>
+      </c>
+      <c r="G94">
+        <v>-2444</v>
+      </c>
+      <c r="H94">
+        <v>-4140</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B95" t="s">
+        <v>63</v>
+      </c>
+      <c r="D95">
+        <v>152</v>
+      </c>
+      <c r="E95">
+        <v>2701</v>
+      </c>
+      <c r="F95">
+        <v>4053</v>
+      </c>
+      <c r="G95">
+        <v>3482</v>
+      </c>
+      <c r="H95">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B96" t="s">
+        <v>64</v>
+      </c>
+      <c r="D96">
+        <v>5348</v>
+      </c>
+      <c r="E96">
+        <v>1162</v>
+      </c>
+      <c r="F96">
+        <v>1964</v>
+      </c>
+      <c r="G96">
+        <v>3516</v>
+      </c>
+      <c r="H96">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" t="s">
+        <v>65</v>
+      </c>
+      <c r="D97">
+        <v>278</v>
+      </c>
+      <c r="E97">
+        <v>-310</v>
+      </c>
+      <c r="F97">
+        <v>126</v>
+      </c>
+      <c r="G97">
+        <v>203</v>
+      </c>
+      <c r="H97">
+        <v>-197</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" t="s">
+        <v>66</v>
+      </c>
+      <c r="D98" s="1">
+        <f>SUM(D84:D97)</f>
+        <v>22174</v>
+      </c>
+      <c r="E98" s="1">
+        <f>SUM(E84:E97)</f>
+        <v>22315</v>
+      </c>
+      <c r="F98" s="1">
+        <f>SUM(F84:F97)</f>
+        <v>26206</v>
+      </c>
+      <c r="G98" s="1">
+        <f>SUM(G84:G97)</f>
+        <v>29068</v>
+      </c>
+      <c r="H98" s="1">
+        <f>SUM(H84:H97)</f>
+        <v>24204</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100">
+        <v>-16577</v>
+      </c>
+      <c r="E100">
+        <v>-17139</v>
+      </c>
+      <c r="F100">
+        <v>-18825</v>
+      </c>
+      <c r="G100">
+        <v>-18314</v>
+      </c>
+      <c r="H100">
+        <v>-27308</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" t="s">
+        <v>69</v>
+      </c>
+      <c r="D101">
+        <v>6489</v>
+      </c>
+      <c r="E101">
+        <v>7045</v>
+      </c>
+      <c r="F101">
+        <v>5907</v>
+      </c>
+      <c r="G101">
+        <v>7307</v>
+      </c>
+      <c r="H101">
+        <v>18514</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B102" t="s">
+        <v>70</v>
+      </c>
+      <c r="D102">
+        <v>7252</v>
+      </c>
+      <c r="E102">
+        <v>8251</v>
+      </c>
+      <c r="F102">
+        <v>6081</v>
+      </c>
+      <c r="G102">
+        <v>9230</v>
+      </c>
+      <c r="H102">
+        <v>9319</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B103" t="s">
+        <v>71</v>
+      </c>
+      <c r="D103">
+        <v>-7139</v>
+      </c>
+      <c r="E103">
+        <v>-4821</v>
+      </c>
+      <c r="F103">
+        <v>-21458</v>
+      </c>
+      <c r="G103">
+        <v>-10136</v>
+      </c>
+      <c r="H103">
+        <v>-13408</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B104" t="s">
+        <v>72</v>
+      </c>
+      <c r="D104">
+        <v>-2051</v>
+      </c>
+      <c r="E104">
+        <v>-2454</v>
+      </c>
+      <c r="F104">
+        <v>-2802</v>
+      </c>
+      <c r="G104">
+        <v>-3386</v>
+      </c>
+      <c r="H104">
+        <v>-3499</v>
+      </c>
+    </row>
+    <row r="105" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B105" t="s">
+        <v>73</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>-9033</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B106" t="s">
+        <v>74</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>4514</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B107" t="s">
+        <v>75</v>
+      </c>
+      <c r="D107">
+        <v>221</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>3414</v>
+      </c>
+      <c r="G107">
+        <v>685</v>
+      </c>
+      <c r="H107">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B108" t="s">
+        <v>59</v>
+      </c>
+      <c r="D108">
+        <v>-727</v>
+      </c>
+      <c r="E108">
+        <v>-1254</v>
+      </c>
+      <c r="F108">
+        <v>-793</v>
+      </c>
+      <c r="G108">
+        <v>-960</v>
+      </c>
+      <c r="H108">
+        <v>-1667</v>
+      </c>
+    </row>
+    <row r="109" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B109" t="s">
+        <v>76</v>
+      </c>
+      <c r="D109">
+        <f>SUM(D100:D108)</f>
+        <v>-12532</v>
+      </c>
+      <c r="E109">
+        <f>SUM(E100:E108)</f>
+        <v>-10372</v>
+      </c>
+      <c r="F109">
+        <f>SUM(F100:F108)</f>
+        <v>-28476</v>
+      </c>
+      <c r="G109">
+        <f>SUM(G100:G108)</f>
+        <v>-15574</v>
+      </c>
+      <c r="H109">
+        <f>SUM(H100:H108)</f>
+        <v>-20527</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B110" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B111" t="s">
+        <v>78</v>
+      </c>
+      <c r="D111">
+        <v>-4250</v>
+      </c>
+      <c r="E111">
+        <v>-5000</v>
+      </c>
+      <c r="F111">
+        <v>-7000</v>
+      </c>
+      <c r="G111">
+        <v>-8000</v>
+      </c>
+      <c r="H111">
+        <v>-9000</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B112" t="s">
+        <v>79</v>
+      </c>
+      <c r="D112">
+        <v>-4584</v>
+      </c>
+      <c r="E112">
+        <v>-5280</v>
+      </c>
+      <c r="F112">
+        <v>-5991</v>
+      </c>
+      <c r="G112">
+        <v>-6761</v>
+      </c>
+      <c r="H112">
+        <v>-7533</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B113" t="s">
+        <v>80</v>
+      </c>
+      <c r="D113">
+        <v>1440</v>
+      </c>
+      <c r="E113">
+        <v>1355</v>
+      </c>
+      <c r="F113">
+        <v>1253</v>
+      </c>
+      <c r="G113">
+        <v>1353</v>
+      </c>
+      <c r="H113">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="114" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B114" t="s">
+        <v>81</v>
+      </c>
+      <c r="D114">
+        <v>-3150</v>
+      </c>
+      <c r="E114">
+        <v>-3150</v>
+      </c>
+      <c r="F114">
+        <v>-3015</v>
+      </c>
+      <c r="G114">
+        <v>-2125</v>
+      </c>
+      <c r="H114">
+        <v>-3000</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B115" t="s">
+        <v>82</v>
+      </c>
+      <c r="D115">
+        <v>872</v>
+      </c>
+      <c r="E115">
+        <v>-1302</v>
+      </c>
+      <c r="F115">
+        <v>732</v>
+      </c>
+      <c r="G115">
+        <v>11</v>
+      </c>
+      <c r="H115">
+        <v>-151</v>
+      </c>
+    </row>
+    <row r="116" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B116" t="s">
+        <v>83</v>
+      </c>
+      <c r="D116">
+        <v>4864</v>
+      </c>
+      <c r="E116">
+        <v>6933</v>
+      </c>
+      <c r="F116">
+        <v>14819</v>
+      </c>
+      <c r="G116">
+        <v>6394</v>
+      </c>
+      <c r="H116">
+        <v>17811</v>
+      </c>
+    </row>
+    <row r="117" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B117" t="s">
+        <v>84</v>
+      </c>
+      <c r="D117">
+        <v>1677</v>
+      </c>
+      <c r="E117">
+        <v>622</v>
+      </c>
+      <c r="F117">
+        <v>5548</v>
+      </c>
+      <c r="G117">
+        <v>-521</v>
+      </c>
+      <c r="H117">
+        <v>-1560</v>
+      </c>
+    </row>
+    <row r="118" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B118" t="s">
+        <v>85</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>-1338</v>
+      </c>
+      <c r="F118">
+        <v>-176</v>
+      </c>
+      <c r="G118">
+        <v>-730</v>
+      </c>
+      <c r="H118">
+        <v>-280</v>
+      </c>
+    </row>
+    <row r="119" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B119" t="s">
+        <v>59</v>
+      </c>
+      <c r="D119">
+        <v>-459</v>
+      </c>
+      <c r="E119">
+        <v>-295</v>
+      </c>
+      <c r="F119">
+        <v>-1944</v>
+      </c>
+      <c r="G119">
+        <v>-1150</v>
+      </c>
+      <c r="H119">
+        <v>-1645</v>
+      </c>
+    </row>
+    <row r="120" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B120" t="s">
+        <v>86</v>
+      </c>
+      <c r="D120">
+        <f>SUM(D111:D119)</f>
+        <v>-3590</v>
+      </c>
+      <c r="E120">
+        <f>SUM(E111:E119)</f>
+        <v>-7455</v>
+      </c>
+      <c r="F120">
+        <f>SUM(F111:F119)</f>
+        <v>4226</v>
+      </c>
+      <c r="G120">
+        <f>SUM(G111:G119)</f>
+        <v>-11529</v>
+      </c>
+      <c r="H120">
+        <f>SUM(H111:H119)</f>
+        <v>-3512</v>
+      </c>
+    </row>
+    <row r="121" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B121" t="s">
+        <v>87</v>
+      </c>
+      <c r="D121">
+        <v>-116</v>
+      </c>
+      <c r="E121">
+        <v>-62</v>
+      </c>
+      <c r="F121">
+        <v>34</v>
+      </c>
+      <c r="G121">
+        <v>97</v>
+      </c>
+      <c r="H121">
+        <v>-61</v>
+      </c>
+    </row>
+    <row r="122" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B122" t="s">
+        <v>88</v>
+      </c>
+      <c r="D122" s="1">
+        <f>D121+D120+D109+D98</f>
+        <v>5936</v>
+      </c>
+      <c r="E122" s="1">
+        <f>E121+E120+E109+E98</f>
+        <v>4426</v>
+      </c>
+      <c r="F122" s="1">
+        <f>F121+F120+F109+F98</f>
+        <v>1990</v>
+      </c>
+      <c r="G122" s="1">
+        <f>G121+G120+G109+G98</f>
+        <v>2062</v>
+      </c>
+      <c r="H122" s="1">
+        <f>H121+H120+H109+H98</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="123" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B123" t="s">
+        <v>89</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>-219</v>
+      </c>
+    </row>
+    <row r="124" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B124" t="s">
+        <v>90</v>
+      </c>
+      <c r="D124" s="1">
+        <f>SUM(D122:D123)</f>
+        <v>5936</v>
+      </c>
+      <c r="E124" s="1">
+        <f>SUM(E122:E123)</f>
+        <v>4426</v>
+      </c>
+      <c r="F124" s="1">
+        <f>SUM(F122:F123)</f>
+        <v>1990</v>
+      </c>
+      <c r="G124" s="1">
+        <f>SUM(G122:G123)</f>
+        <v>2062</v>
+      </c>
+      <c r="H124" s="1">
+        <f>SUM(H122:H123)</f>
+        <v>-115</v>
+      </c>
+    </row>
+    <row r="125" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B125" t="s">
+        <v>91</v>
+      </c>
+      <c r="D125">
+        <v>10985</v>
+      </c>
+      <c r="E125">
+        <f>D126</f>
+        <v>16921</v>
+      </c>
+      <c r="F125">
+        <f>E23</f>
+        <v>21375</v>
+      </c>
+      <c r="G125">
+        <f>F23</f>
+        <v>23365</v>
+      </c>
+      <c r="H125">
+        <f>G23</f>
+        <v>25427</v>
+      </c>
+    </row>
+    <row r="126" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B126" t="s">
+        <v>92</v>
+      </c>
+      <c r="D126" s="1">
+        <f>D125+D124</f>
+        <v>16921</v>
+      </c>
+      <c r="E126" s="1">
+        <f>E125+E124</f>
+        <v>21347</v>
+      </c>
+      <c r="F126" s="1">
+        <f>F125+F124</f>
+        <v>23365</v>
+      </c>
+      <c r="G126" s="1">
+        <f>G125+G124</f>
+        <v>25427</v>
+      </c>
+      <c r="H126" s="1">
+        <f>H125+H124</f>
+        <v>25312</v>
+      </c>
+    </row>
+    <row r="127" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B127" t="s">
+        <v>149</v>
+      </c>
+      <c r="D127">
+        <f>D23</f>
+        <v>16921</v>
+      </c>
+      <c r="E127">
+        <f>E23</f>
+        <v>21375</v>
+      </c>
+      <c r="F127">
+        <f>F23</f>
+        <v>23365</v>
+      </c>
+      <c r="G127">
+        <f>G23</f>
+        <v>25427</v>
+      </c>
+      <c r="H127">
+        <f>H23</f>
+        <v>25312</v>
+      </c>
+    </row>
+    <row r="128" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B128" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="129" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B129" t="s">
+        <v>94</v>
+      </c>
+      <c r="D129">
+        <v>1704</v>
+      </c>
+      <c r="F129">
+        <v>1945</v>
+      </c>
+      <c r="G129">
+        <v>3035</v>
+      </c>
+      <c r="H129">
+        <v>3594</v>
+      </c>
+    </row>
+    <row r="130" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B130" t="s">
+        <v>95</v>
+      </c>
+      <c r="D130">
+        <v>4935</v>
+      </c>
+      <c r="F130">
+        <v>5222</v>
+      </c>
+      <c r="G130">
+        <v>6078</v>
+      </c>
+      <c r="H130">
+        <v>4620</v>
+      </c>
+    </row>
+    <row r="150" spans="2:25" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
+      <c r="E150" s="1"/>
+      <c r="F150" s="1"/>
+      <c r="G150" s="1"/>
+      <c r="H150" s="1"/>
+    </row>
+    <row r="151" spans="2:25" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="J151" s="41"/>
+      <c r="K151" s="41"/>
+      <c r="L151" s="41"/>
+      <c r="M151" s="41"/>
+      <c r="S151" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="T20" s="26"/>
-    </row>
-    <row r="21" spans="2:80" x14ac:dyDescent="0.55000000000000004">
-      <c r="I21" s="42"/>
-      <c r="S21" s="49" t="s">
+      <c r="T151" s="26"/>
+    </row>
+    <row r="152" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="I152" s="42"/>
+      <c r="S152" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="T21" s="50">
+      <c r="T152" s="50">
         <v>0.01</v>
       </c>
     </row>
-    <row r="22" spans="2:80" x14ac:dyDescent="0.55000000000000004">
-      <c r="S22" s="34" t="s">
+    <row r="153" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="S153" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="T22" s="51">
+      <c r="T153" s="51">
         <v>7.8200000000000006E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B23" t="s">
+    <row r="154" spans="2:25" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B154" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="8">
-        <f t="shared" ref="C23:H23" si="42">C13/C7</f>
+      <c r="C154" s="8">
+        <f>C13/C7</f>
         <v>8.1290908715492147E-2</v>
       </c>
-      <c r="D23" s="8">
-        <f t="shared" si="42"/>
+      <c r="D154" s="8">
+        <f>D13/D7</f>
         <v>8.7131184836334932E-2</v>
       </c>
-      <c r="E23" s="8">
-        <f t="shared" si="42"/>
+      <c r="E154" s="8">
+        <f>E13/E7</f>
         <v>8.3345792897700596E-2</v>
       </c>
-      <c r="F23" s="8">
-        <f t="shared" si="42"/>
+      <c r="F154" s="8">
+        <f>F13/F7</f>
         <v>8.7718486435794454E-2</v>
       </c>
-      <c r="G23" s="8">
-        <f t="shared" si="42"/>
+      <c r="G154" s="8">
+        <f>G13/G7</f>
         <v>8.7072347708155057E-2</v>
       </c>
-      <c r="H23" s="8">
-        <f t="shared" si="42"/>
+      <c r="H154" s="8">
+        <f>H13/H7</f>
         <v>8.0661440298992207E-2</v>
       </c>
-      <c r="S23" s="33" t="s">
+      <c r="S154" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="T23" s="59">
-        <f>NPV(T22,H17:CV17)</f>
+      <c r="T154" s="59">
+        <f>NPV(T153,H17:CV17)</f>
         <v>617527.17800957547</v>
       </c>
     </row>
-    <row r="24" spans="2:80" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" t="s">
+    <row r="155" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B155" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="8">
-        <f t="shared" ref="C24:H24" si="43">C17/C7</f>
+      <c r="C155" s="8">
+        <f>C17/C7</f>
         <v>5.8801181061716667E-2</v>
       </c>
-      <c r="D24" s="8">
-        <f t="shared" si="43"/>
+      <c r="D155" s="8">
+        <f>D17/D7</f>
         <v>6.1324331786840686E-2</v>
       </c>
-      <c r="E24" s="8">
-        <f t="shared" si="43"/>
+      <c r="E155" s="8">
+        <f>E17/E7</f>
         <v>6.1655719635462125E-2</v>
       </c>
-      <c r="F24" s="8">
-        <f t="shared" si="43"/>
+      <c r="F155" s="8">
+        <f>F17/F7</f>
         <v>6.3668782892504369E-2</v>
       </c>
-      <c r="G24" s="8">
-        <f t="shared" si="43"/>
+      <c r="G155" s="8">
+        <f>G17/G7</f>
         <v>6.2278336589330019E-2</v>
       </c>
-      <c r="H24" s="8">
-        <f t="shared" si="43"/>
+      <c r="H155" s="8">
+        <f>H17/H7</f>
         <v>3.8078535417884571E-2</v>
       </c>
-      <c r="S24" s="49" t="s">
+      <c r="S155" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="T24" s="60">
-        <f>T23/EV!E6</f>
+      <c r="T155" s="60">
+        <f>T154/EV!E6</f>
         <v>681.84302727583372</v>
       </c>
     </row>
-    <row r="25" spans="2:80" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" t="s">
+    <row r="156" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B156" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8">
+      <c r="C156" s="8"/>
+      <c r="D156" s="8">
         <f>D7/C7-1</f>
         <v>6.1885982118890848E-2</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E156" s="8">
         <f>E7/D7-1</f>
         <v>0.11844085540617799</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F156" s="8">
         <f>F7/E7-1</f>
         <v>0.12713971286209524</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G156" s="8">
         <f>G7/F7-1</f>
         <v>0.14640827734281014</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H156" s="8">
         <f>H7/G7-1</f>
         <v>7.7110612396467326E-2</v>
       </c>
-      <c r="S25" s="34" t="s">
+      <c r="S156" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="T25" s="61">
+      <c r="T156" s="61">
         <v>359.66</v>
       </c>
     </row>
-    <row r="26" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B26" t="s">
+    <row r="157" spans="2:25" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B157" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8">
+      <c r="C157" s="8"/>
+      <c r="D157" s="8">
         <f>D12/C12-1</f>
         <v>5.5135523890861737E-2</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E157" s="8">
         <f>E12/D12-1</f>
         <v>0.12307869265898708</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F157" s="8">
         <f>F12/E12-1</f>
         <v>0.12176294537357712</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G157" s="8">
         <f>G12/F12-1</f>
         <v>0.14722024028918557</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H157" s="8">
         <f>H12/G12-1</f>
         <v>8.4674471797774098E-2</v>
       </c>
-      <c r="S26" s="33" t="str">
-        <f>IF(T26&gt;=0,"Underpriced","Overpriced")</f>
+      <c r="S157" s="33" t="str">
+        <f>IF(T157&gt;=0,"Underpriced","Overpriced")</f>
         <v>Underpriced</v>
       </c>
-      <c r="T26" s="52">
-        <f>T24-T25</f>
+      <c r="T157" s="52">
+        <f>T155-T156</f>
         <v>322.18302727583369</v>
       </c>
     </row>
-    <row r="27" spans="2:80" x14ac:dyDescent="0.55000000000000004">
-      <c r="D27" s="8">
+    <row r="158" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="D158" s="8">
         <f>(D17/C17)-1</f>
         <v>0.10745136596671112</v>
       </c>
-      <c r="E27" s="8">
-        <f t="shared" ref="E27:H27" si="44">(E17/D17)-1</f>
+      <c r="E158" s="8">
+        <f>(E17/D17)-1</f>
         <v>0.12448474855729597</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F158" s="8">
+        <f>(F17/E17)-1</f>
+        <v>0.16394089781186549</v>
+      </c>
+      <c r="G158" s="8">
+        <f>(G17/F17)-1</f>
+        <v>0.12137215950385194</v>
+      </c>
+      <c r="H158" s="8">
+        <f>(H17/G17)-1</f>
+        <v>-0.34142758382302107</v>
+      </c>
+    </row>
+    <row r="159" spans="2:25" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="160" spans="2:25" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B160" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="C160" s="44"/>
+      <c r="D160" s="44"/>
+      <c r="E160" s="44"/>
+      <c r="F160" s="44"/>
+      <c r="G160" s="44"/>
+      <c r="H160" s="44"/>
+      <c r="I160" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="S160" s="67" t="s">
+        <v>50</v>
+      </c>
+      <c r="T160" s="68"/>
+      <c r="U160" s="68"/>
+      <c r="V160" s="68"/>
+      <c r="W160" s="68"/>
+      <c r="X160" s="68"/>
+      <c r="Y160" s="69"/>
+    </row>
+    <row r="161" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B161" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="D161" s="41">
+        <f t="shared" ref="D161:H172" si="42">D3/C3-1</f>
+        <v>6.2093105393280945E-2</v>
+      </c>
+      <c r="E161" s="41">
+        <f t="shared" si="42"/>
+        <v>0.12286701277558842</v>
+      </c>
+      <c r="F161" s="41">
+        <f t="shared" si="42"/>
+        <v>0.13669093368341478</v>
+      </c>
+      <c r="G161" s="41">
+        <f t="shared" si="42"/>
+        <v>0.13093168764606844</v>
+      </c>
+      <c r="H161" s="41">
+        <f t="shared" si="42"/>
+        <v>6.1834011285059498E-2</v>
+      </c>
+      <c r="I161" s="45">
+        <f>AVERAGE(D161:H161)</f>
+        <v>0.10288335015668242</v>
+      </c>
+      <c r="S161" s="70"/>
+      <c r="T161" s="71"/>
+      <c r="U161" s="71"/>
+      <c r="V161" s="71"/>
+      <c r="W161" s="71"/>
+      <c r="X161" s="71"/>
+      <c r="Y161" s="72"/>
+    </row>
+    <row r="162" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B162" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D162" s="41">
+        <f t="shared" si="42"/>
+        <v>8.0640567142450159E-2</v>
+      </c>
+      <c r="E162" s="41">
+        <f t="shared" si="42"/>
+        <v>8.5517645336066206E-3</v>
+      </c>
+      <c r="F162" s="41">
+        <f t="shared" si="42"/>
+        <v>8.6738101460638317E-2</v>
+      </c>
+      <c r="G162" s="41">
+        <f t="shared" si="42"/>
+        <v>0.13785271483539985</v>
+      </c>
+      <c r="H162" s="41">
+        <f t="shared" si="42"/>
+        <v>0.17948477091797188</v>
+      </c>
+      <c r="I162" s="45">
+        <f t="shared" ref="I162:I174" si="43">AVERAGE(D162:H162)</f>
+        <v>9.8653583778013365E-2</v>
+      </c>
+      <c r="S162" s="70"/>
+      <c r="T162" s="71"/>
+      <c r="U162" s="71"/>
+      <c r="V162" s="71"/>
+      <c r="W162" s="71"/>
+      <c r="X162" s="71"/>
+      <c r="Y162" s="72"/>
+    </row>
+    <row r="163" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B163" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D163" s="41">
+        <f t="shared" si="42"/>
+        <v>5.4972856164022588E-2</v>
+      </c>
+      <c r="E163" s="41">
+        <f t="shared" si="42"/>
+        <v>0.22916666666666674</v>
+      </c>
+      <c r="F163" s="41">
+        <f t="shared" si="42"/>
+        <v>0.1198227858391252</v>
+      </c>
+      <c r="G163" s="41">
+        <f t="shared" si="42"/>
+        <v>0.23853943595513782</v>
+      </c>
+      <c r="H163" s="41">
+        <f t="shared" si="42"/>
+        <v>5.6179116724789813E-2</v>
+      </c>
+      <c r="I163" s="45">
+        <f t="shared" si="43"/>
+        <v>0.13973617226994844</v>
+      </c>
+      <c r="S163" s="70"/>
+      <c r="T163" s="71"/>
+      <c r="U163" s="71"/>
+      <c r="V163" s="71"/>
+      <c r="W163" s="71"/>
+      <c r="X163" s="71"/>
+      <c r="Y163" s="72"/>
+    </row>
+    <row r="164" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B164" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="41">
+        <f t="shared" si="42"/>
+        <v>-0.2036055143160127</v>
+      </c>
+      <c r="E164" s="41">
+        <f t="shared" si="42"/>
+        <v>0.54727030625832218</v>
+      </c>
+      <c r="F164" s="41">
+        <f t="shared" si="42"/>
+        <v>-0.12650602409638556</v>
+      </c>
+      <c r="G164" s="41">
+        <f t="shared" si="42"/>
+        <v>1.0142857142857142</v>
+      </c>
+      <c r="H164" s="41">
+        <f t="shared" si="42"/>
+        <v>0.27219369038884822</v>
+      </c>
+      <c r="I164" s="45">
+        <f t="shared" si="43"/>
+        <v>0.30072763450409729</v>
+      </c>
+      <c r="S164" s="70"/>
+      <c r="T164" s="71"/>
+      <c r="U164" s="71"/>
+      <c r="V164" s="71"/>
+      <c r="W164" s="71"/>
+      <c r="X164" s="71"/>
+      <c r="Y164" s="72"/>
+    </row>
+    <row r="165" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B165" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D165" s="54">
+        <f t="shared" si="42"/>
+        <v>6.1885982118890848E-2</v>
+      </c>
+      <c r="E165" s="54">
+        <f t="shared" si="42"/>
+        <v>0.11844085540617799</v>
+      </c>
+      <c r="F165" s="54">
+        <f t="shared" si="42"/>
+        <v>0.12713971286209524</v>
+      </c>
+      <c r="G165" s="54">
+        <f t="shared" si="42"/>
+        <v>0.14640827734281014</v>
+      </c>
+      <c r="H165" s="54">
+        <f t="shared" si="42"/>
+        <v>7.7110612396467326E-2</v>
+      </c>
+      <c r="I165" s="55">
+        <f t="shared" si="43"/>
+        <v>0.10619708802528831</v>
+      </c>
+      <c r="S165" s="70"/>
+      <c r="T165" s="71"/>
+      <c r="U165" s="71"/>
+      <c r="V165" s="71"/>
+      <c r="W165" s="71"/>
+      <c r="X165" s="71"/>
+      <c r="Y165" s="72"/>
+    </row>
+    <row r="166" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B166" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D166" s="41">
+        <f t="shared" si="42"/>
+        <v>1.8895423165430802E-2</v>
+      </c>
+      <c r="E166" s="41">
+        <f t="shared" si="42"/>
+        <v>0.17262039197972356</v>
+      </c>
+      <c r="F166" s="41">
+        <f t="shared" si="42"/>
+        <v>0.12803419809428007</v>
+      </c>
+      <c r="G166" s="41">
+        <f t="shared" si="42"/>
+        <v>0.14727615939898131</v>
+      </c>
+      <c r="H166" s="41">
+        <f t="shared" si="42"/>
+        <v>9.215193431833768E-2</v>
+      </c>
+      <c r="I166" s="45">
+        <f t="shared" si="43"/>
+        <v>0.11179562139135069</v>
+      </c>
+      <c r="O166" s="63"/>
+      <c r="P166" s="63"/>
+      <c r="Q166" s="63"/>
+      <c r="R166" s="63"/>
+      <c r="S166" s="73"/>
+      <c r="T166" s="74"/>
+      <c r="U166" s="74"/>
+      <c r="V166" s="74"/>
+      <c r="W166" s="74"/>
+      <c r="X166" s="74"/>
+      <c r="Y166" s="75"/>
+    </row>
+    <row r="167" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B167" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="D167" s="41">
+        <f t="shared" si="42"/>
+        <v>0.18500838234876249</v>
+      </c>
+      <c r="E167" s="41">
+        <f t="shared" si="42"/>
+        <v>2.0981200844043757E-2</v>
+      </c>
+      <c r="F167" s="41">
+        <f t="shared" si="42"/>
+        <v>0.12219638789074416</v>
+      </c>
+      <c r="G167" s="41">
+        <f t="shared" si="42"/>
+        <v>0.14327571051860533</v>
+      </c>
+      <c r="H167" s="41">
+        <f t="shared" si="42"/>
+        <v>-2.956359376144102E-2</v>
+      </c>
+      <c r="I167" s="45">
+        <f t="shared" si="43"/>
+        <v>8.8379617568142943E-2</v>
+      </c>
+      <c r="O167" s="63"/>
+      <c r="P167" s="63"/>
+      <c r="Q167" s="63"/>
+      <c r="R167" s="63"/>
+      <c r="S167" s="63"/>
+      <c r="T167" s="63"/>
+      <c r="U167" s="63"/>
+      <c r="V167" s="63"/>
+      <c r="W167" s="63"/>
+    </row>
+    <row r="168" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B168" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D168" s="41">
+        <f t="shared" si="42"/>
+        <v>9.3466586051143441E-2</v>
+      </c>
+      <c r="E168" s="41">
+        <f t="shared" si="42"/>
+        <v>9.3999024231581352E-3</v>
+      </c>
+      <c r="F168" s="41">
+        <f t="shared" si="42"/>
+        <v>8.6002448926983277E-2</v>
+      </c>
+      <c r="G168" s="41">
+        <f t="shared" si="42"/>
+        <v>0.15034269946295575</v>
+      </c>
+      <c r="H168" s="41">
+        <f t="shared" si="42"/>
+        <v>0.2043848336342533</v>
+      </c>
+      <c r="I168" s="45">
+        <f t="shared" si="43"/>
+        <v>0.10871929409969878</v>
+      </c>
+    </row>
+    <row r="169" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B169" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D169" s="41">
+        <f t="shared" si="42"/>
+        <v>6.2867647058823639E-2</v>
+      </c>
+      <c r="E169" s="41">
+        <f t="shared" si="42"/>
+        <v>7.3331027326184683E-2</v>
+      </c>
+      <c r="F169" s="41">
+        <f t="shared" si="42"/>
+        <v>9.5713825330325575E-2</v>
+      </c>
+      <c r="G169" s="41">
+        <f t="shared" si="42"/>
+        <v>0.16823529411764704</v>
+      </c>
+      <c r="H169" s="41">
+        <f t="shared" si="42"/>
+        <v>3.1973816717019155E-2</v>
+      </c>
+      <c r="I169" s="45">
+        <f t="shared" si="43"/>
+        <v>8.6424322110000021E-2</v>
+      </c>
+    </row>
+    <row r="170" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B170" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D170" s="54">
+        <f t="shared" si="42"/>
+        <v>5.5135523890861737E-2</v>
+      </c>
+      <c r="E170" s="54">
+        <f t="shared" si="42"/>
+        <v>0.12307869265898708</v>
+      </c>
+      <c r="F170" s="54">
+        <f t="shared" si="42"/>
+        <v>0.12176294537357712</v>
+      </c>
+      <c r="G170" s="54">
+        <f t="shared" si="42"/>
+        <v>0.14722024028918557</v>
+      </c>
+      <c r="H170" s="54">
+        <f t="shared" si="42"/>
+        <v>8.4674471797774098E-2</v>
+      </c>
+      <c r="I170" s="55">
+        <f t="shared" si="43"/>
+        <v>0.10637437480207712</v>
+      </c>
+    </row>
+    <row r="171" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B171" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D171" s="54">
+        <f t="shared" si="42"/>
+        <v>0.1381762763525527</v>
+      </c>
+      <c r="E171" s="54">
+        <f t="shared" si="42"/>
+        <v>6.9850479803615251E-2</v>
+      </c>
+      <c r="F171" s="54">
+        <f t="shared" si="42"/>
+        <v>0.18627450980392157</v>
+      </c>
+      <c r="G171" s="54">
+        <f t="shared" si="42"/>
+        <v>0.13796377703534368</v>
+      </c>
+      <c r="H171" s="54">
+        <f t="shared" si="42"/>
+        <v>-2.1942023610853623E-3</v>
+      </c>
+      <c r="I171" s="55">
+        <f t="shared" si="43"/>
+        <v>0.10601416812686956</v>
+      </c>
+    </row>
+    <row r="172" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B172" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D172" s="41">
+        <f t="shared" si="42"/>
+        <v>-2.4061032863849752E-2</v>
+      </c>
+      <c r="E172" s="41">
+        <f t="shared" si="42"/>
+        <v>-1.8039687312086938E-3</v>
+      </c>
+      <c r="F172" s="41">
+        <f t="shared" si="42"/>
+        <v>0.26024096385542173</v>
+      </c>
+      <c r="G172" s="41">
+        <f t="shared" si="42"/>
+        <v>0.55162523900573612</v>
+      </c>
+      <c r="H172" s="41">
+        <f t="shared" si="42"/>
+        <v>0.20332717190388161</v>
+      </c>
+      <c r="I172" s="45">
+        <f t="shared" si="43"/>
+        <v>0.19786567463399621</v>
+      </c>
+    </row>
+    <row r="173" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B173" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D173" s="41"/>
+      <c r="E173" s="41"/>
+      <c r="F173" s="41"/>
+      <c r="G173" s="41"/>
+      <c r="H173" s="41"/>
+      <c r="I173" s="45"/>
+    </row>
+    <row r="174" spans="2:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="B174" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D174" s="41">
+        <f t="shared" ref="D174:H175" si="44">D16/C16-1</f>
+        <v>0.32896846606093</v>
+      </c>
+      <c r="E174" s="41">
+        <f t="shared" si="44"/>
+        <v>-7.9428916147194828E-2</v>
+      </c>
+      <c r="F174" s="41">
+        <f t="shared" si="44"/>
+        <v>0.24595893403232849</v>
+      </c>
+      <c r="G174" s="41">
+        <f t="shared" si="44"/>
+        <v>4.628330995792429E-2</v>
+      </c>
+      <c r="H174" s="41">
+        <f t="shared" si="44"/>
+        <v>-0.1908512064343163</v>
+      </c>
+      <c r="I174" s="45">
+        <f t="shared" si="43"/>
+        <v>7.018611749393433E-2</v>
+      </c>
+    </row>
+    <row r="175" spans="2:25" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B175" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="C175" s="48"/>
+      <c r="D175" s="56">
+        <f t="shared" si="44"/>
+        <v>0.10745136596671112</v>
+      </c>
+      <c r="E175" s="56">
+        <f t="shared" si="44"/>
+        <v>0.12448474855729597</v>
+      </c>
+      <c r="F175" s="56">
         <f t="shared" si="44"/>
         <v>0.16394089781186549</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G175" s="56">
         <f t="shared" si="44"/>
         <v>0.12137215950385194</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H175" s="56">
         <f t="shared" si="44"/>
         <v>-0.34142758382302107</v>
       </c>
-    </row>
-    <row r="28" spans="2:80" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="29" spans="2:80" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B29" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="S29" s="67" t="s">
-        <v>50</v>
-      </c>
-      <c r="T29" s="68"/>
-      <c r="U29" s="68"/>
-      <c r="V29" s="68"/>
-      <c r="W29" s="68"/>
-      <c r="X29" s="68"/>
-      <c r="Y29" s="69"/>
-    </row>
-    <row r="30" spans="2:80" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="D30" s="41">
-        <f t="shared" ref="D30:H41" si="45">D3/C3-1</f>
-        <v>6.2093105393280945E-2</v>
-      </c>
-      <c r="E30" s="41">
-        <f t="shared" si="45"/>
-        <v>0.12286701277558842</v>
-      </c>
-      <c r="F30" s="41">
-        <f t="shared" si="45"/>
-        <v>0.13669093368341478</v>
-      </c>
-      <c r="G30" s="41">
-        <f t="shared" si="45"/>
-        <v>0.13093168764606844</v>
-      </c>
-      <c r="H30" s="41">
-        <f t="shared" si="45"/>
-        <v>6.1834011285059498E-2</v>
-      </c>
-      <c r="I30" s="45">
-        <f>AVERAGE(D30:H30)</f>
-        <v>0.10288335015668242</v>
-      </c>
-      <c r="S30" s="70"/>
-      <c r="T30" s="71"/>
-      <c r="U30" s="71"/>
-      <c r="V30" s="71"/>
-      <c r="W30" s="71"/>
-      <c r="X30" s="71"/>
-      <c r="Y30" s="72"/>
-    </row>
-    <row r="31" spans="2:80" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="41">
-        <f t="shared" si="45"/>
-        <v>8.0640567142450159E-2</v>
-      </c>
-      <c r="E31" s="41">
-        <f t="shared" si="45"/>
-        <v>8.5517645336066206E-3</v>
-      </c>
-      <c r="F31" s="41">
-        <f t="shared" si="45"/>
-        <v>8.6738101460638317E-2</v>
-      </c>
-      <c r="G31" s="41">
-        <f t="shared" si="45"/>
-        <v>0.13785271483539985</v>
-      </c>
-      <c r="H31" s="41">
-        <f t="shared" si="45"/>
-        <v>0.17948477091797188</v>
-      </c>
-      <c r="I31" s="45">
-        <f t="shared" ref="I31:I44" si="46">AVERAGE(D31:H31)</f>
-        <v>9.8653583778013365E-2</v>
-      </c>
-      <c r="S31" s="70"/>
-      <c r="T31" s="71"/>
-      <c r="U31" s="71"/>
-      <c r="V31" s="71"/>
-      <c r="W31" s="71"/>
-      <c r="X31" s="71"/>
-      <c r="Y31" s="72"/>
-    </row>
-    <row r="32" spans="2:80" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="D32" s="41">
-        <f t="shared" si="45"/>
-        <v>5.4972856164022588E-2</v>
-      </c>
-      <c r="E32" s="41">
-        <f t="shared" si="45"/>
-        <v>0.22916666666666674</v>
-      </c>
-      <c r="F32" s="41">
-        <f t="shared" si="45"/>
-        <v>0.1198227858391252</v>
-      </c>
-      <c r="G32" s="41">
-        <f t="shared" si="45"/>
-        <v>0.23853943595513782</v>
-      </c>
-      <c r="H32" s="41">
-        <f t="shared" si="45"/>
-        <v>5.6179116724789813E-2</v>
-      </c>
-      <c r="I32" s="45">
-        <f t="shared" si="46"/>
-        <v>0.13973617226994844</v>
-      </c>
-      <c r="S32" s="70"/>
-      <c r="T32" s="71"/>
-      <c r="U32" s="71"/>
-      <c r="V32" s="71"/>
-      <c r="W32" s="71"/>
-      <c r="X32" s="71"/>
-      <c r="Y32" s="72"/>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="41">
-        <f t="shared" si="45"/>
-        <v>-0.2036055143160127</v>
-      </c>
-      <c r="E33" s="41">
-        <f t="shared" si="45"/>
-        <v>0.54727030625832218</v>
-      </c>
-      <c r="F33" s="41">
-        <f t="shared" si="45"/>
-        <v>-0.12650602409638556</v>
-      </c>
-      <c r="G33" s="41">
-        <f t="shared" si="45"/>
-        <v>1.0142857142857142</v>
-      </c>
-      <c r="H33" s="41">
-        <f t="shared" si="45"/>
-        <v>0.27219369038884822</v>
-      </c>
-      <c r="I33" s="45">
-        <f t="shared" si="46"/>
-        <v>0.30072763450409729</v>
-      </c>
-      <c r="S33" s="70"/>
-      <c r="T33" s="71"/>
-      <c r="U33" s="71"/>
-      <c r="V33" s="71"/>
-      <c r="W33" s="71"/>
-      <c r="X33" s="71"/>
-      <c r="Y33" s="72"/>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" s="54">
-        <f t="shared" si="45"/>
-        <v>6.1885982118890848E-2</v>
-      </c>
-      <c r="E34" s="54">
-        <f t="shared" si="45"/>
-        <v>0.11844085540617799</v>
-      </c>
-      <c r="F34" s="54">
-        <f t="shared" si="45"/>
-        <v>0.12713971286209524</v>
-      </c>
-      <c r="G34" s="54">
-        <f t="shared" si="45"/>
-        <v>0.14640827734281014</v>
-      </c>
-      <c r="H34" s="54">
-        <f t="shared" si="45"/>
-        <v>7.7110612396467326E-2</v>
-      </c>
-      <c r="I34" s="55">
-        <f t="shared" si="46"/>
-        <v>0.10619708802528831</v>
-      </c>
-      <c r="S34" s="70"/>
-      <c r="T34" s="71"/>
-      <c r="U34" s="71"/>
-      <c r="V34" s="71"/>
-      <c r="W34" s="71"/>
-      <c r="X34" s="71"/>
-      <c r="Y34" s="72"/>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="41">
-        <f t="shared" si="45"/>
-        <v>1.8895423165430802E-2</v>
-      </c>
-      <c r="E35" s="41">
-        <f t="shared" si="45"/>
-        <v>0.17262039197972356</v>
-      </c>
-      <c r="F35" s="41">
-        <f t="shared" si="45"/>
-        <v>0.12803419809428007</v>
-      </c>
-      <c r="G35" s="41">
-        <f t="shared" si="45"/>
-        <v>0.14727615939898131</v>
-      </c>
-      <c r="H35" s="41">
-        <f t="shared" si="45"/>
-        <v>9.215193431833768E-2</v>
-      </c>
-      <c r="I35" s="45">
-        <f t="shared" si="46"/>
-        <v>0.11179562139135069</v>
-      </c>
-      <c r="O35" s="66"/>
-      <c r="P35" s="66"/>
-      <c r="Q35" s="66"/>
-      <c r="R35" s="66"/>
-      <c r="S35" s="73"/>
-      <c r="T35" s="74"/>
-      <c r="U35" s="74"/>
-      <c r="V35" s="74"/>
-      <c r="W35" s="74"/>
-      <c r="X35" s="74"/>
-      <c r="Y35" s="75"/>
-    </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="41">
-        <f t="shared" si="45"/>
-        <v>0.18500838234876249</v>
-      </c>
-      <c r="E36" s="41">
-        <f t="shared" si="45"/>
-        <v>2.0981200844043757E-2</v>
-      </c>
-      <c r="F36" s="41">
-        <f t="shared" si="45"/>
-        <v>0.12219638789074416</v>
-      </c>
-      <c r="G36" s="41">
-        <f t="shared" si="45"/>
-        <v>0.14327571051860533</v>
-      </c>
-      <c r="H36" s="41">
-        <f t="shared" si="45"/>
-        <v>-2.956359376144102E-2</v>
-      </c>
-      <c r="I36" s="45">
-        <f t="shared" si="46"/>
-        <v>8.8379617568142943E-2</v>
-      </c>
-      <c r="O36" s="66"/>
-      <c r="P36" s="66"/>
-      <c r="Q36" s="66"/>
-      <c r="R36" s="66"/>
-      <c r="S36" s="66"/>
-      <c r="T36" s="66"/>
-      <c r="U36" s="66"/>
-      <c r="V36" s="66"/>
-      <c r="W36" s="66"/>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="41">
-        <f t="shared" si="45"/>
-        <v>9.3466586051143441E-2</v>
-      </c>
-      <c r="E37" s="41">
-        <f t="shared" si="45"/>
-        <v>9.3999024231581352E-3</v>
-      </c>
-      <c r="F37" s="41">
-        <f t="shared" si="45"/>
-        <v>8.6002448926983277E-2</v>
-      </c>
-      <c r="G37" s="41">
-        <f t="shared" si="45"/>
-        <v>0.15034269946295575</v>
-      </c>
-      <c r="H37" s="41">
-        <f t="shared" si="45"/>
-        <v>0.2043848336342533</v>
-      </c>
-      <c r="I37" s="45">
-        <f t="shared" si="46"/>
-        <v>0.10871929409969878</v>
-      </c>
-    </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="41">
-        <f t="shared" si="45"/>
-        <v>6.2867647058823639E-2</v>
-      </c>
-      <c r="E38" s="41">
-        <f t="shared" si="45"/>
-        <v>7.3331027326184683E-2</v>
-      </c>
-      <c r="F38" s="41">
-        <f t="shared" si="45"/>
-        <v>9.5713825330325575E-2</v>
-      </c>
-      <c r="G38" s="41">
-        <f t="shared" si="45"/>
-        <v>0.16823529411764704</v>
-      </c>
-      <c r="H38" s="41">
-        <f t="shared" si="45"/>
-        <v>3.1973816717019155E-2</v>
-      </c>
-      <c r="I38" s="45">
-        <f t="shared" si="46"/>
-        <v>8.6424322110000021E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="54">
-        <f t="shared" si="45"/>
-        <v>5.5135523890861737E-2</v>
-      </c>
-      <c r="E39" s="54">
-        <f t="shared" si="45"/>
-        <v>0.12307869265898708</v>
-      </c>
-      <c r="F39" s="54">
-        <f t="shared" si="45"/>
-        <v>0.12176294537357712</v>
-      </c>
-      <c r="G39" s="54">
-        <f t="shared" si="45"/>
-        <v>0.14722024028918557</v>
-      </c>
-      <c r="H39" s="54">
-        <f t="shared" si="45"/>
-        <v>8.4674471797774098E-2</v>
-      </c>
-      <c r="I39" s="55">
-        <f t="shared" si="46"/>
-        <v>0.10637437480207712</v>
-      </c>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="54">
-        <f t="shared" si="45"/>
-        <v>0.1381762763525527</v>
-      </c>
-      <c r="E40" s="54">
-        <f t="shared" si="45"/>
-        <v>6.9850479803615251E-2</v>
-      </c>
-      <c r="F40" s="54">
-        <f t="shared" si="45"/>
-        <v>0.18627450980392157</v>
-      </c>
-      <c r="G40" s="54">
-        <f t="shared" si="45"/>
-        <v>0.13796377703534368</v>
-      </c>
-      <c r="H40" s="54">
-        <f t="shared" si="45"/>
-        <v>-2.1942023610853623E-3</v>
-      </c>
-      <c r="I40" s="55">
-        <f t="shared" si="46"/>
-        <v>0.10601416812686956</v>
-      </c>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="41">
-        <f t="shared" si="45"/>
-        <v>-2.4061032863849752E-2</v>
-      </c>
-      <c r="E41" s="41">
-        <f t="shared" si="45"/>
-        <v>-1.8039687312086938E-3</v>
-      </c>
-      <c r="F41" s="41">
-        <f t="shared" si="45"/>
-        <v>0.26024096385542173</v>
-      </c>
-      <c r="G41" s="41">
-        <f t="shared" si="45"/>
-        <v>0.55162523900573612</v>
-      </c>
-      <c r="H41" s="41">
-        <f t="shared" si="45"/>
-        <v>0.20332717190388161</v>
-      </c>
-      <c r="I41" s="45">
-        <f t="shared" si="46"/>
-        <v>0.19786567463399621</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="45"/>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" s="41">
-        <f t="shared" ref="D43:H44" si="47">D16/C16-1</f>
-        <v>0.32896846606093</v>
-      </c>
-      <c r="E43" s="41">
-        <f t="shared" si="47"/>
-        <v>-7.9428916147194828E-2</v>
-      </c>
-      <c r="F43" s="41">
-        <f t="shared" si="47"/>
-        <v>0.24595893403232849</v>
-      </c>
-      <c r="G43" s="41">
-        <f t="shared" si="47"/>
-        <v>4.628330995792429E-2</v>
-      </c>
-      <c r="H43" s="41">
-        <f t="shared" si="47"/>
-        <v>-0.1908512064343163</v>
-      </c>
-      <c r="I43" s="45">
-        <f t="shared" si="46"/>
-        <v>7.018611749393433E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="2:25" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B44" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="48"/>
-      <c r="D44" s="56">
-        <f t="shared" si="47"/>
-        <v>0.10745136596671112</v>
-      </c>
-      <c r="E44" s="56">
-        <f t="shared" si="47"/>
-        <v>0.12448474855729597</v>
-      </c>
-      <c r="F44" s="56">
-        <f t="shared" si="47"/>
-        <v>0.16394089781186549</v>
-      </c>
-      <c r="G44" s="56">
-        <f t="shared" si="47"/>
-        <v>0.12137215950385194</v>
-      </c>
-      <c r="H44" s="56">
-        <f t="shared" si="47"/>
-        <v>-0.34142758382302107</v>
-      </c>
-      <c r="I44" s="57">
-        <f>AVERAGE(D44:H44)</f>
+      <c r="I175" s="57">
+        <f>AVERAGE(D175:H175)</f>
         <v>3.516431760334069E-2</v>
       </c>
-      <c r="J44" s="41"/>
-    </row>
-    <row r="49" spans="9:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="I49" s="42"/>
-      <c r="J49" s="42"/>
-      <c r="K49" s="42"/>
-      <c r="L49" s="42"/>
-      <c r="M49" s="42"/>
-      <c r="N49" s="42"/>
-      <c r="O49" s="42"/>
-      <c r="P49" s="42"/>
-      <c r="Q49" s="42"/>
-      <c r="R49" s="42"/>
+      <c r="J175" s="41"/>
+    </row>
+    <row r="180" spans="9:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="I180" s="42"/>
+      <c r="J180" s="42"/>
+      <c r="K180" s="42"/>
+      <c r="L180" s="42"/>
+      <c r="M180" s="42"/>
+      <c r="N180" s="42"/>
+      <c r="O180" s="42"/>
+      <c r="P180" s="42"/>
+      <c r="Q180" s="42"/>
+      <c r="R180" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="S29:Y35"/>
+    <mergeCell ref="S160:Y166"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="MAIN!A1" tooltip="click to travel to main page" display="MAIN" xr:uid="{111E8870-67FD-4E3C-8020-90F6F8E485FD}"/>
